--- a/file_service/qabul.xlsx
+++ b/file_service/qabul.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M237"/>
+  <dimension ref="A1:M256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.42578125" customWidth="1" min="1" max="1"/>
@@ -13941,6 +13941,1089 @@
         </is>
       </c>
     </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Xusenov Anis Naufarovich</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Rus tili</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>AD3186658</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>50206066110072</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Samarqand viloyati</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Samarqand tumani</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>998950904404</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>+998950904404</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Quziboyev Mehriddin Jaxongirovich</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>AD8538383</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>50112075650028</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Qashqadaryo viloyati</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Qarshi tumani</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>998955253313</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>+998914743435</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Solijonov obidjon axror ogli</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>AE1978187</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>50606086820106</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Toshkent viloyati</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Yangiyoʻl tumani</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>998994028939</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>+998953510002</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Mingboshiyev Behro'z Dilshod o'g'li</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>AD4356766</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>51601076410036</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Sirdaryo viloyati</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Guliston tumani</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>998944234434</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>+998944234434</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Raimjonova Aminabonu</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>AD0405710</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>62505056730047</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Olmazor tumani</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>998935182505</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>+998935182505</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Saidov Lazizbek Latifjon ogli</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>AD3132398</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>50304076930069</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Mirzo Ulugʻbek tumani</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>998881420703</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>+998881420703</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Yoldoshov Ulugbek Anvarovich</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>AD8274466</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>50408085320032</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Yunusobod tumani</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>998941220359</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>+998994198080</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Axmedova Mavsuma Yaxshiboevna</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Psixologiya</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>AD4026627</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>41807843990014</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Samarqand viloyati</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Urgut tumani</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>998979268084</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>+998979268084</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Asrolova Ezoza Bobir qizi</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>AD4405589</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>62108075520044</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Jizzax viloyati</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Forish tumani</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>998954647007</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>+998954647007</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Urakov Dilmurod</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Mehnat muhofazasi va texnika xavfsizligi</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>AD3864089</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>52806075850028</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Navoiy viloyati</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Zarafshon shahri</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>998931129716</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>+998931129716</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Sultonmurodova Sevinch Sanjarovna</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Rus tili</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>AD4231746</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>62306076840026</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Toshkent viloyati</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Angren shahri</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>998933233122</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>+998936683122</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Rizayeva Nigoraxon Sadikovna</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Mehnat muhofazasi va texnika xavfsizligi</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Rus tili</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>AD6008106</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>42511841230032</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Andijon viloyati</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Andijon shahri</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>998889941720</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>+998884222261</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Yusupjonova Sevinch</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Rus tili</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>AE3369465</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>61608066560040</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Sergeli tumani</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>998974235989</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>+998971432402</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Aslonova Sabrina</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>AD8337762</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>62108075790045</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Navoiy viloyati</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Navoiy shahri</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>998936637874</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>+998936637874</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Shukurullayev Adham Javlonbekovich</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>AD5041031</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>53110076100017</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Navoiy viloyati</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Navoiy shahri</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>998930029066</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>+998970869066</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Pirmahammatov Fazliddin Sherali ogli</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>AD5610246</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>50409075720119</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Mirzo Ulugʻbek tumani</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>998944135002</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>+998333003917</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Narzullayev shaxzod sherali ogli</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Hayot faoliyati xavfsizligi</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>AD8513979</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>52101086510018</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Mirobod tumani</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>998337212108</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>+998337212108</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Shodiqulov shohruh shahobiddinovich</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Rus tili</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>AD9483081</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>50704085800027</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Navoiy viloyati</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Nurota tumani</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>998507190002</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>+998507190002</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Mirzaboyev Javoxir</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Metrologiya va standartlashtirish</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>AD4390816</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>30207976690023</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Toshkent viloyati</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Oqqoʻrgʻon tumani</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>998975470704</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>+998975470704</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="D1:D66"/>
   <mergeCells count="1">

--- a/file_service/qabul.xlsx
+++ b/file_service/qabul.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M256"/>
+  <dimension ref="A1:M393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.42578125" customWidth="1" min="1" max="1"/>
@@ -15024,6 +15024,7800 @@
         </is>
       </c>
     </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>kamalatdinov Ilhamitdin</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>AD3178875</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>50601087270019</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Qoraqalpogʻiston Respublikasi</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Qanlikoʻl tumani</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>998907003693</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>+998907003693</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Isroilov Murodulla</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>AD8523562</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>50604075540024</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Jizzax viloyati</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Jizzax shahri</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>998974842939</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>+998930615779</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Ikramova Xursand Aslonovna</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Mehnat muhofazasi va texnika xavfsizligi</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>AB2724546</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>41706842400019</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Navoiy viloyati</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Zarafshon shahri</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>998937773506</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>+998919918485</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Ibragimov Abbos Hamdamovich</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>AD5633332</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>31109884180012</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Fargona viloyati</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Beshariq tumani</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>998507018378</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>+998930457444</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Isamuhamedova Robiya Erkin qizi</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Psixologiya</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>AD1693725</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>61507006500080</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Uchtepa tumani</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>998951188616</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>+998909458616</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Omonkeldiyev Asadbek Alisher o'g'li</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>AB6461089</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>50405005420014</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Jizzax viloyati</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Jizzax shahri</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>998945711700</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>+998200047100</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Nurmatova Mohfira</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>AD3917418</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>62604067130049</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Xorazm viloyati</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Urganch tumani</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>998773161983</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>+998936341708</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Ochilova Ismigul Obidjon qizi</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>AD1837891</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>60807015820050</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Navoiy viloyati</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Karmana tumani</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>998952772808</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>+998952772808</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Yaqubov Husan Xayrilla O'g'li</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Menejment</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>AD2470717</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>51603056020048</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Samarqand viloyati</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Oqdaryo tumani</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>+998930640381</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>+998952110476</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>A'zamov  Bobomurod  Zarif O'g'li</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>AE1445789</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>51212075790045</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Navoiy viloyati</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Navbahor tumani</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>998997193036</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>+998973224847</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Nurullayev Ozodbek Jasurbek o'g'li</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Ijtimoiy ish</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>AD7223680</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>50705085590051</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Sergeli tumani</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>998887567772</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>+998887567772</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Rasulov Abdumomin</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Inson resurslarini boshqarish</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>AD4526332</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>52508075210010</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Andijon viloyati</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Xoʻjaobod tumani</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>998940620140</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>+998940620140</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Aminbayev Firdavs Xursand o'g'li</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>AD7013697</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>51507077250032</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Qoraqalpogʻiston Respublikasi</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Ellikqalʼa tumani</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>998990693007</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>+998773393029</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Asadov G'aybullo Sadilloyevich</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Menejment</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>AD6734231</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>67342315894123</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Kogon tumani</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>+998939601100</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>+998933834818</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Rakhimov Qudrat Qurbonovich</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Psixologiya</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>AB9210249</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>50583111007642</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Kogon tumani</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>+998939601100</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>+998933834818</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Djaksimuratov Diyorbek</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Bugalteriya hisobi</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>AD4867250</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>51709077360108</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Qoraqalpogʻiston Respublikasi</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>Qoʻngʻirot tumani</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>998937710015</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>+998937710015</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Jyenbekov Qabiljan Mubarekvich</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Menejment</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>AD7648729</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>51605007300019</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Qoraqalpogʻiston Respublikasi</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>Taxtakoʻpir tumani</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>998955531484</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>+998952268714</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Tilovov sanjar</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>AD4756257</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>52109076250034</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Surxondaryo viloyati</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Qiziriq tumani</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>998976941104</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>+998954144607</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Hakimov shahridin</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>AD9722333</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>50507076280044</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Surxondaryo viloyati</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Sherobod tumani</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>998947683186</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>+998937683186</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Anvarov Ahadxon Azizjon ugli</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Rus tili</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>AD4545285</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>51403075840032</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Navoiy viloyati</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>Karmana tumani</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>998942860004</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>+998942860004</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Jorayev jorabek shokirjon o'g'li</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Hayot faoliyati xavfsizligi</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>AD4105738</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>50606056790064</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Toshkent viloyati</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>Piskent</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>998943072820</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>+998943072820</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Diyorbek Hamroyev</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>AD6251176</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>53103075710026</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Qashqadaryo viloyati</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>Mirishkor tumani</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>998975854043</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>+998770246132</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Abdusattorov Boburbek Nurbek o'g'li</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Inson resurslarini boshqarish</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>AD7933406</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>52007076830015</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Toshkent viloyati</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Olmaliq shahri</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>998942970066</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>+998942970066</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Sodiqova Shahzoda Otabek qizi</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>AD6299645</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>61807075800044</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Navoiy viloyati</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>Nurota tumani</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>998991969785</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>+998501042947</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Elshod farhatov dilshod o'g'li</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>AD5077937</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>52806066050040</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Mirzo Ulugʻbek tumani</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>998930862829</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>+998930862829</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Qabulova Rayhon Rashid qizi</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>AB1165082</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>41110933120010</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Xorazm viloyati</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>Xonqa tumani</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>998937573131</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>+998937573131</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Akimniyazova Dilbar Tolibaevna</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Menejment</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>AD5078250</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>40103883430051</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Qoraqalpogʻiston Respublikasi</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>Chimboy tumani</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>998975096256</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>+998975096256</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Mardon xurramov ilhom ogli</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>AE2584546</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>52610076280023</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Mirzo Ulugʻbek tumani</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>998774578888</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>+998951081131</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Raupova Zebo Abdullayevna</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Inson resurslarini boshqarish</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>AD1383975</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>42805876500014</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>Mirzo Ulugʻbek tumani</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>+998977163339</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>+998712330454</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Karimova Mashhura Oybek qizi</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>AD6418827</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>62211065500026</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Jizzax viloyati</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>Zafarobod tumani</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>998943443103</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>+998991486050</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Karimboyeva Sitorabonu Baxtishod qizi</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Inson resurslarini boshqarish</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>AD0592416</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>61708056610026</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>Yashnaobod tumani</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>998773783132</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>+998773783132</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Sattorov Farrux Turaqulovich</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>AE1971953</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>32612872560037</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Qashqadaryo viloyati</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>+998919524908</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>+998977132226</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Abduraxmanov Javoxir Jasurovich</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Rus tili</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>AD4588626</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>52803076600018</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>Mirzo Ulugʻbek tumani</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>998909343091</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>+998777670078</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Akbaraliyeva odina</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>AD8897772</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>61807086700036</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>Chilonzor tumani</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>998932586955</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>+998933857227</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Sayfullayeva Marjona Nurilla qizi</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Ijtimoiy ish</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>AD9251466</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>61706076030039</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Samarqand viloyati</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>Bulungʻur tumani</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>998904783626</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>+998937249115</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Abdusattorov Bexruz Muxammadjon o'g'li</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Inson resurslarini boshqarish</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>AD4715532</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>51205076730024</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Toshkent viloyati</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>Boʻka tumani</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>998509995907</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>+998509995907</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Raimqulova Kamola Sobirovna</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>AD6966946</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>60311076270010</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Surxondaryo viloyati</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>Termiz shahri</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>998507702650</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>+998507702650</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Iskandarova Dinara Ikramovna</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Ijtimoiy ish</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>AD4643670</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>42608883080027</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Xorazm viloyati</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>Gurlan tumani</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>998997342608</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>+998997342608</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Qahhorov Shahriyor Yodgorovich</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>AC2631337</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>31105941890063</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>Surxondaryo viloyati</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>Angor tumani</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>998996471820</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>+998996471820</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Jumabaeva Aytgul Jubatxanovna</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Bugalteriya hisobi</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>AD9297743</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>62012077360044</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Qoraqalpogʻiston Respublikasi</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>Qoʻngʻirot tumani</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>998882240760</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>+998882240760</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Xudoyberdiyev Xurshid Farhod ogli</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>AD7391601</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>50709076450029</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>Sirdaryo viloyati</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>Guliston shahri</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>998936105606</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>+998936105606</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Tojimboyev Azizbek Baxodir o'g'li</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>AD5529401</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>51211076720046</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>Toshkent viloyati</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>Boʻstonliq tumani</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>+998942132161</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>+998931992161</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Ibragimova Nigora Abdurauf qizi</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>AD4104357</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>43103930170021</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>Mirzo Ulugʻbek tumani</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>998990321116</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>+998994401116</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Rozzoqov Zafar Qoshnazarovich</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>AB4679653</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>30807913070011</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>Xorazm viloyati</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>Bogʻot tumani</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>998905790575</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>+998335585505</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Ruzimurodov Elchinbek Yaqub ogli</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>AD5081459</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>51512065720059</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>Qashqadaryo viloyati</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>Chiroqchi tumani</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>998997226406</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>+998973846507</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Qaxramonov Abdullohon</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>AD5542019</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>52111077050045</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>Mirzo Ulugʻbek tumani</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>998933777258</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>+998933777258</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Qo'shnazarov sarvar shavkatboy o'g'li</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>AD4940641</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>52807077100025</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>Chilonzor tumani</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>998772042707</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>+998772042707</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Kuatov Tohir Abdumutalovich</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>AD6230778</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>50512066410011</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>Sirdaryo viloyati</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>Guliston shahri</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>998943547892</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>+998937898683</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Odil Zairov</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>AD6791830</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>52002086820065</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>Yakkasaroy tumani</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>998338085251</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>+998337826022</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Azimova Madinaxon Fathulla qizi</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>AD5179900</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>61211076750068</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>Chilonzor tumani</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>998903514454</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>+998909900999</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Asadullayeva Ezoza Laziz qizi</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>AD4841069</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>62709076740059</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>Toshkent viloyati</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Yuqori Chirchiq tumani</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>998993470927</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>+998949452717</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Buvajonova Mavludaxon Saminjon qizi</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>AD9553901</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>60304076950015</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>Fargona viloyati</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>Uchkoʻprik tumani</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>998903431701</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>+998916870343</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Saparboyeva Shahruzaxon Temurbek qizi</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>AD8086463</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>61205077140070</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>Xorazm viloyati</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>Hazorasp tumani</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>998882215747</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>+998977670512</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>A A Yusuf</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>AB9973074</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>50906026610052</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Olmazor tumani</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>998998707042</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>+998999091110</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Axrorov Yusuf Axrorovich</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>AB9973070</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>50906026610052</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Olmazor tumani</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>998998707042</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>+998999091110</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Uktamova Rayxona Asqarjon qizi</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>AD6526151</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>61602085590013</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>Qashqadaryo viloyati</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>998979681101</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>+998979681101</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Yaxshimuratova Sevinchoy Bozorboy qizi</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>AC2990955</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>61703047110015</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>Xorazm viloyati</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>Gurlan tumani</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>79050634034</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>+998941179890</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Xamidov Xasan Jurahon ogli</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>AD1757536</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>52002066610086</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>Olmazor tumani</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>998900217879</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>+998983003231</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Abdumannopov Olloberdi Ilxomjon  o'g'li</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>AC2972779</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>52708045160046</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>Andijon viloyati</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>Oltinkoʻl tuman</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>998775714877</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>+998775714877</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Pulatov Bobir Bafoyevich</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>AE1829017</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>33011911110052</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>Jondor tumani</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>+998934576466</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>+998934576466</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Namozova Zuxra</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Psixologiya</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>AC1205473</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>60906025340024</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Romitan tumani</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>998936253110</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>+998936413110</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Rustamov Jamhurbek</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Mehnat muhofazasi va texnika xavfsizligi</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>AC0330528</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>51908025370019</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>Qorovulbozor tumani</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>998993507137</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>+998993507137</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Zokirov Javohir Zohiddin o'g'li</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>AD3192790</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>51805065650030</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>Qashqadaryo viloyati</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>Qarshi tumani</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>998900700309</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>+998900700309</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Xolmominov Sherzod Botir ogli</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>AC2016257</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>51004035410014</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>Sirdaryo viloyati</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>Oqoltin tumani</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>998942515203</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>+998936297779</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Yodgorova Nargiza Tairovna</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Ijtimoiy ish</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>AD5539197</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>40204805310012</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>Gʻijduvon tumani</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>998919257881</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>+998934728300</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Ispanov Jangabay Turganbaevich</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>KA0780163</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>31506773470012</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>Qoraqalpogʻiston Respublikasi</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>Qoʻngʻirot tumani</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>998999521399</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>+998937140155</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Jumanov Aktam Ibodullayevich</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Psixologiya</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>AB2279907</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>31511803980025</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>Toshkent viloyati</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>Ohangaron tumani</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>+998946661195</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>+998946261980</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Qoraxonov Nodirjon</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>AD0223821</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>52508045630062</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>Qashqadaryo viloyati</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>Qamashi tumani</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>998906767202</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>+998906767202</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>dovronov abdulaziz asqarali ogli</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Mehnat muhofazasi va texnika xavfsizligi</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>AD9036702</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>52808075610017</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>Qashqadaryo viloyati</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>Dehqonobod tumani</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>998942377545</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>+998943997678</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Bafoyeva Sidiqa Xamroyevna</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Ijtimoiy ish</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>AA3199418</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>42711721140011</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>Kogon tumani</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>+998939601100</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>+998935548989</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Rasulova Zulfizar Saidovna</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Psixologiya</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>AA0872485</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>41803911140037</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>Kogon tumani</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>+998939601100</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>+998917849581</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Ziyodilloyev Azizbek Navroz ogli</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>AE2578010</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>51204065340055</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>Romitan tumani</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>998889744404</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>+998913100234</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Shuhrat Iskandarov Jahongirovich</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>AD6737477</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>51011075590024</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>Qashqadaryo viloyati</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>998938005068</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>+998930579449</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Nematilloyev Azizbek Azamatjonovich</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Mehnat muhofazasi va texnika xavfsizligi</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>AD5104042</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>52005075260066</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>Buxoro tumani</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>998934550859</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>+998906118771</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Vafoyev Boburmirzo Qahramon ogli</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>AC1849508</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>50902025320013</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>Qorakoʻl tumani</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>998337470909</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>+998947567556</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Norov Bexruz Axror o'g'li</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Menejment</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>AC2310633</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>51811035260037</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>Buxoro tumani</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>+998914095252</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>+998907458113</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>ASADOVA SABOHAT O'KTAM QIZI</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Psixologiya</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>AC1558705</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>41912911050038</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>Buxoro tumani</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>+998914095252</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>+998914145959</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Qahorova Samira Jamshedovna</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Menejment</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>AD2814877</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>61104065260078</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>Buxoro tumani</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>998918331554</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>+998905113705</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>RUSTAMOVA TURSUNOY TUYMURODOVNA</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>AD7777573</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>50612075310060</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>Gʻijduvon tumani</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>+998916473180</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>+998912434322</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>To'xtayeva Oydinoy Kamolovna</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Psixologiya</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>AD2760082</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>43003881070071</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>Gʻijduvon tumani</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>998907104555</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>+998907104555</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Raxmidinov Xayotbek Ozod O'g'li</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>AD7913254</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>53103086520090</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>Toshkent viloyati</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>Qibray tumani</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>998977173103</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>+998977173103</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Djamalov Jalolbek Oybekovich</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Rus tili</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>AD4540540</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>50509076170035</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>Yashnaobod tumani</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>998972850123</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>+998979201234</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Sharopov Javoxir Jahongirovich</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Menejment</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>AD8817586</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>52607075280024</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>Buxoro tumani</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>+998939601100</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>+998948647848</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Toxirov Tolibjon Tolibovich</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Bugalteriya hisobi</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>AD4278781</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>50210075280013</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>Buxoro tumani</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>998943239727</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>+998914182588</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Zokirova Feruzabonu</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Inson resurslarini boshqarish</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>AD7905276</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>60607076610078</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>Sergeli tumani</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>998774048633</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>+998774048633</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Murodova Maxsuna Najmiddin qizi</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Psixologiya</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>AD4784304</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>61808075720088</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>Chilonzor tumani</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>998944281822</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>+998939278727</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Muhammadiyeva Dilnoza Sobirovna</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Psixologiya</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>AD4164065</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>61807076600038</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>Mirzo Ulugʻbek tumani</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>998335153115</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>+998333390022</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Umaraliyev Zuhriddin Nuriddin ogli</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>AD1611400</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>50708056910029</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>Fargona viloyati</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>Bagʻdod tumani</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>998941899966</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>+998941899966</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Sayidova Munis Sheraliyevna</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>AD1433274</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>00410005590037</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>Qashqadaryo viloyati</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>998908838855</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>+998908838855</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Safarova Nilufar Xamidovna</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Ijtimoiy ish</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>AD3628706</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>41203128504202</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>Buxoro tumani</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>+998939601100</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>+998914428652</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Itolmasova Maloxat Naimovna</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>AD3695885</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>41203872568001</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>Buxoro tumani</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>+998939601100</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>+998975612325</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>KOROTAYEVA LYUDMILA GENNADEVNA</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Psixologiya</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>AD4249853</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>60802075300027</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>Buxoro tumani</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>+998914095252</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>+998914058555</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Najmetdinova Rayxona Jamshedovna</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Psixologiya</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>AD8253766</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>60509075260019</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>Buxoro tumani</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>998918331554</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>+998918331554</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>O'tkurov Javdod Uchkurovich</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Rus tili</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>AE3501540</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>30210986610075</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>Olmazor tumani</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>998974010133</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>+998991220088</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Qobilov Malik Muhitdin ogli</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Menejment</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>AB4037076</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>32104911060018</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>Vobkent tumani</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>998914097878</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>+998914097878</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Axmatov Farxod Furqatovich</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Menejment</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>AB2768268</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>32409985260057</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>Vobkent tumani</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>+998971462626</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>+998980072626</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Djumanova Gulnora Mirzaliyevna</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>AD5411751</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>43012826860017</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>Toshkent viloyati</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>Chirchiq shahri</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>998917760347</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>+998917760347</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Qoryogdiyev Elnur Jalil ogli</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Hayot faoliyati xavfsizligi</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>AB6200043</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>52403005320020</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>Buxoro tumani</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>998337470909</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>+998932902266</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Raxmonov Sardorbek Ikrom ogli</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Hayot faoliyati xavfsizligi</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>AE1148018</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>31012965320024</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>Buxoro tumani</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>998337470909</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>+998332700909</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Murodov Ozodbek Tojiddin ogli</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Ijtimoiy ish</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>AB5148515</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>52004005320012</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>Qorakoʻl tumani</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>998337470909</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>+998337470909</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Ismatov Sardor Sunnatovich</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>AB7035087</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>51204015360061</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>Buxoro tumani</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>998934501860</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>+998944501860</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Turdiyev Mirjalol Vaxob o'g'li</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Rus tili</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>AD3840053</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>31912933940064</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>Bektemir tumani</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>+998950208757</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>+998900162400</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Egamberdiyeva Sarvinoz Shavkatovna</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Inson resurslarini boshqarish</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>AD8881372</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>61204086620010</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>Mirzo Ulugʻbek tumani</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>998935236622</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>+998946201474</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Salimov Mamurjon Iskandarovich</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>AD1925742</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>52809066150019</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>Samarqand viloyati</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>Toyloq tumani</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>998886158603</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>+998886158603</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Bayzaqov Mirmuhsin Rasuljon ogli</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Metrologiya va standartlashtirish</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>AD8882474</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>50302086450052</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>Sirdaryo viloyati</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>Guliston tumani</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>998700177208</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>+998994420382</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Ulugbekov Sardor Ulugbek ogli</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>AD9943736</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>51103070005071</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>Mirzo Ulugʻbek tumani</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>998938290504</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>+998953342332</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Tursunboyeva Ziyoda Xamid qizi</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>AD4317736</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>60107076620018</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>Mirzo Ulugʻbek tumani</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>998908147557</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>+998908147557</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>SAMANDAROVA SOGDIANA MUHIDDIN QIZI</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Psixologiya</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>AE2177737</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>60802075300027</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>Buxoro tumani</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>+998904140403</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>+998914058555</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Boynazarova Hosila</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>AD2026343</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>60806065730010</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>Qashqadaryo viloyati</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>Yakkabogʻ tumani</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>998902445506</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>+998974510506</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>RAXMONOV XURSHIDBEK NODIROVICH</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Hayot faoliyati xavfsizligi</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>AD4158952</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>41212945896574</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>Kogon tumani</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>+998914095252</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>+998936262286</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>ELMURODOV OZODBEK OTABEKOVICH</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Bugalteriya hisobi</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>AD4105390</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>31506985680412</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>Kogon tumani</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>+998914095252</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>+998995257645</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>TUXTAYEVA AMINABONU QAHRAMON QIZI</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Psixologiya</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>AB8254776</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>41312941000013</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>Buxoro tumani</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>+998914095252</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>+998934630600</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>PO'LOTOV ISTAM RAMAZONOVICH</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>AE3149883</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>31807925280016</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>Buxoro tumani</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>+998914095252</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>+998945490605</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Quvvatova Ruxshona</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Psixologiya</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>AD9049048</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>61412076790016</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>Toshkent viloyati</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>Piskent tumani</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>998950592978</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>+998950741214</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Trofimova Evelina Vladimirovna</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Rus tili</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>AD3695493</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>61706076590036</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>Uchtepa tumani</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>998903217238</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>+998990644666</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Xusanboyev Mirjalol Baxodir ogli</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>AD4655876</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>52003076780017</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>Toshkent viloyati</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>Qibray tumani</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>998974041076</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>+998880780320</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Ergashev Shohjaxon</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>AD5186284</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>52406075740071</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>Qashqadaryo viloyati</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>Qarshi tumani</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>998914697007</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>+998900837017</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Kamolov Shoxboz Baxtiyor ogli</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Ijtimoiy ish</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>AD7842133</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>51611076790025</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>Toshkent viloyati</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>Piskent tumani</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>998887311611</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>+998887311611</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Salimov Jahongir Samad ogli</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>AD9447133</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>50110075290040</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>Vobkent tumani</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>998990788664</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>+998502422040</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Rajabova Sevinch Anvar qizi</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Psixologiya</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>AD9047497</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>62212075780031</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>Kogon tumani</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>998991255019</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>+998503015040</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Sayfuddinov Dalerbek  Doniyorovich</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>AD5281217</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>52711075380049</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>Kogon tumani</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>998991255019</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>+998991255019</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Xumoyun Orifjonov Ortiqboy ovich</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Mehnat muhofazasi va texnika xavfsizligi</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>AD3790938</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>52204076790019</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>Toshkent viloyati</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>Olmaliq shahri</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>998936219621</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>+998936219621</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Nizomiddinova Munavvar Ilxom qizi</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>AD7603396</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>60106066100033</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>Samarqand viloyati</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>Paxtachi tumani</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>998939522203</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>+998939522203</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Mastonov Shamshod Mansur o'g'li</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Bugalteriya hisobi</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>AB1962400</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>32304961050025</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>Buxoro tumani</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>998914041013</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>+998995899981</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Axrorov Sarvar Anvarivich</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>AD6794891</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>51408076130043</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>Samarqand viloyati</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>Urgut tumani</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>998904640232</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>+998904640232</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Saloxitdinova Durdona Sur'atjon qizi</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>AD7978684</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>60410076130088</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>Samarqand viloyati</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>Urgut tumani</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>998902710233</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>+998952733407</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Arabboyev Javlonbek</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>AD1846631</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>50707055880076</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>Namangan viloyati</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>Namangan tumani</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>998936672524</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>+998936672524</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Obidov Sarvarbek Sadriddin ogli</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>AD8610812</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>51308075310061</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>Buxoro viloyati</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>Gʻijduvon tumani</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>998931759619</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>+998907315567</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Yusupov Odilbek Oybek ogli</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Bugalteriya hisobi</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>AD3433993</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>52104076520024</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>Yunusobod tumani</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>998900531581</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>+998903221581</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Masharifov masharif murod ogli</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>AD4081861</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>51212057130018</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>Xorazm viloyati</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>Urganch tumani</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>998200056838</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>+998918686838</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Sharipova Shaxnoza Ravshan kizi</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Inson resurslarini boshqarish</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>AD7979208</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>63009076590027</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>Yangihayot tumani</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>+998977309054</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>+998977309054</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Teshaeva zulfizarbonu</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Bugalteriya hisobi</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>AC0437935</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>41202659003002</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>Chilonzor tumani</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>998934258101</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>+998979004444</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Teshayeva Aminabonu Baxtiyorovna</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>AD6502161</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>62412075260072</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>Chilonzor tumani</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>998880063663</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>+998880063663</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Imamov Aydar Damirovich</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Rus tili</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>AD4738493</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>50609076750139</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>Olmazor tumani</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>998770788957</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>+998330080844</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Obidov Asilbek Tohir ogli</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>AD0986511</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>50812056810066</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>Toshkent viloyati</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>Chinoz tumani</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>998888744144</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>+998901193090</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Fozilova Saodat Soxib Qizi</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>AD7623885</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>60402075540023</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>Jizzax viloyati</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>Jizzax shahri</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>998974402178</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>+998902977782</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Temur Xodjiyev</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>AD5613988</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>52411076730031</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>Toshkent viloyati</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>Piskent tumani</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>998956600737</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>+998999433004</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="D1:D66"/>
   <mergeCells count="1">

--- a/file_service/qabul.xlsx
+++ b/file_service/qabul.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M478"/>
+  <dimension ref="A1:M487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.42578125" customWidth="1" min="1" max="1"/>
@@ -18903,12 +18903,12 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>dovronov abdulaziz asqarali ogli</t>
+          <t>Bafoyeva Sidiqa Xamroyevna</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Mehnat muhofazasi va texnika xavfsizligi</t>
+          <t>Ijtimoiy ish</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -18923,32 +18923,32 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>AD9036702</t>
+          <t>AA3199418</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>52808075610017</t>
+          <t>42711721140011</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Qashqadaryo viloyati</t>
+          <t>Buxoro viloyati</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>Dehqonobod tumani</t>
+          <t>Kogon tumani</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>998942377545</t>
+          <t>+998939601100</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>+998943997678</t>
+          <t>+998935548989</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
@@ -18960,12 +18960,12 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Bafoyeva Sidiqa Xamroyevna</t>
+          <t>Rasulova Zulfizar Saidovna</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Ijtimoiy ish</t>
+          <t>Psixologiya</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -18980,12 +18980,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>AA3199418</t>
+          <t>AA0872485</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>42711721140011</t>
+          <t>41803911140037</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
@@ -19005,7 +19005,7 @@
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>+998935548989</t>
+          <t>+998917849581</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
@@ -19017,12 +19017,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Rasulova Zulfizar Saidovna</t>
+          <t>Ziyodilloyev Azizbek Navroz ogli</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Psixologiya</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -19037,12 +19037,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>AA0872485</t>
+          <t>AE2578010</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>41803911140037</t>
+          <t>51204065340055</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -19052,17 +19052,17 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>Kogon tumani</t>
+          <t>Romitan tumani</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>+998939601100</t>
+          <t>998889744404</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>+998917849581</t>
+          <t>+998913100234</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
@@ -19074,7 +19074,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Ziyodilloyev Azizbek Navroz ogli</t>
+          <t>Shuhrat Iskandarov Jahongirovich</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -19094,32 +19094,32 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>AE2578010</t>
+          <t>AD6737477</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>51204065340055</t>
+          <t>51011075590024</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Buxoro viloyati</t>
+          <t>Qashqadaryo viloyati</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Romitan tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>998889744404</t>
+          <t>998938005068</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>+998913100234</t>
+          <t>+998930579449</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
@@ -19131,12 +19131,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Shuhrat Iskandarov Jahongirovich</t>
+          <t>Nematilloyev Azizbek Azamatjonovich</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Mehnat muhofazasi va texnika xavfsizligi</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -19151,32 +19151,32 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>AD6737477</t>
+          <t>AD5104042</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>51011075590024</t>
+          <t>52005075260066</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Qashqadaryo viloyati</t>
+          <t>Buxoro viloyati</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Buxoro tumani</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>998938005068</t>
+          <t>998934550859</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>+998930579449</t>
+          <t>+998906118771</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
@@ -19188,12 +19188,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Nematilloyev Azizbek Azamatjonovich</t>
+          <t>Vafoyev Boburmirzo Qahramon ogli</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Mehnat muhofazasi va texnika xavfsizligi</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -19208,12 +19208,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>AD5104042</t>
+          <t>AC1849508</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>52005075260066</t>
+          <t>50902025320013</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
@@ -19223,17 +19223,17 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>Buxoro tumani</t>
+          <t>Qorakoʻl tumani</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>998934550859</t>
+          <t>998337470909</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>+998906118771</t>
+          <t>+998947567556</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
@@ -19245,12 +19245,12 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Vafoyev Boburmirzo Qahramon ogli</t>
+          <t>Norov Bexruz Axror o'g'li</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Menejment</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -19265,12 +19265,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>AC1849508</t>
+          <t>AC2310633</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>50902025320013</t>
+          <t>51811035260037</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
@@ -19280,17 +19280,17 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>Qorakoʻl tumani</t>
+          <t>Buxoro tumani</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>998337470909</t>
+          <t>+998914095252</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>+998947567556</t>
+          <t>+998907458113</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
@@ -19302,12 +19302,12 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Norov Bexruz Axror o'g'li</t>
+          <t>ASADOVA SABOHAT O'KTAM QIZI</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Menejment</t>
+          <t>Psixologiya</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -19322,12 +19322,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>AC2310633</t>
+          <t>AC1558705</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>51811035260037</t>
+          <t>41912911050038</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
@@ -19347,7 +19347,7 @@
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>+998907458113</t>
+          <t>+998914145959</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
@@ -19359,12 +19359,12 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>ASADOVA SABOHAT O'KTAM QIZI</t>
+          <t>Qahorova Samira Jamshedovna</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Psixologiya</t>
+          <t>Menejment</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -19379,12 +19379,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>AC1558705</t>
+          <t>AD2814877</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>41912911050038</t>
+          <t>61104065260078</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
@@ -19399,12 +19399,12 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>+998914095252</t>
+          <t>998918331554</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>+998914145959</t>
+          <t>+998905113705</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
@@ -19416,12 +19416,12 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Qahorova Samira Jamshedovna</t>
+          <t>RUSTAMOVA TURSUNOY TUYMURODOVNA</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Menejment</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -19436,12 +19436,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>AD2814877</t>
+          <t>AD7777573</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>61104065260078</t>
+          <t>50612075310060</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
@@ -19451,17 +19451,17 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Buxoro tumani</t>
+          <t>Gʻijduvon tumani</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>998918331554</t>
+          <t>+998916473180</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>+998905113705</t>
+          <t>+998912434322</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
@@ -19473,12 +19473,12 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>RUSTAMOVA TURSUNOY TUYMURODOVNA</t>
+          <t>To'xtayeva Oydinoy Kamolovna</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Psixologiya</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -19493,12 +19493,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>AD7777573</t>
+          <t>AD2760082</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>50612075310060</t>
+          <t>43003881070071</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
@@ -19513,12 +19513,12 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>+998916473180</t>
+          <t>998907104555</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>+998912434322</t>
+          <t>+998907104555</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
@@ -19530,12 +19530,12 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>To'xtayeva Oydinoy Kamolovna</t>
+          <t>Raxmidinov Xayotbek Ozod O'g'li</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Psixologiya</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -19550,32 +19550,32 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>AD2760082</t>
+          <t>AD7913254</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>43003881070071</t>
+          <t>53103086520090</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Buxoro viloyati</t>
+          <t>Toshkent viloyati</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Gʻijduvon tumani</t>
+          <t>Qibray tumani</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>998907104555</t>
+          <t>998977173103</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>+998907104555</t>
+          <t>+998977173103</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
@@ -19587,7 +19587,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Raxmidinov Xayotbek Ozod O'g'li</t>
+          <t>Djamalov Jalolbek Oybekovich</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -19597,7 +19597,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>O'zbek tili</t>
+          <t>Rus tili</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -19607,32 +19607,32 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>AD7913254</t>
+          <t>AD4540540</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>53103086520090</t>
+          <t>50509076170035</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Toshkent viloyati</t>
+          <t>Toshkent shahri</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Qibray tumani</t>
+          <t>Yashnaobod tumani</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>998977173103</t>
+          <t>998972850123</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>+998977173103</t>
+          <t>+998979201234</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
@@ -19644,17 +19644,17 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Djamalov Jalolbek Oybekovich</t>
+          <t>Sharopov Javoxir Jahongirovich</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Menejment</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Rus tili</t>
+          <t>O'zbek tili</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -19664,49 +19664,49 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>AD4540540</t>
+          <t>AD8817586</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>50509076170035</t>
+          <t>52607075280024</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Toshkent shahri</t>
+          <t>Buxoro viloyati</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Yashnaobod tumani</t>
+          <t>Buxoro tumani</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>998972850123</t>
+          <t>+998939601100</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>+998979201234</t>
+          <t>+998948647848</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Sharopov Javoxir Jahongirovich</t>
+          <t>Toxirov Tolibjon Tolibovich</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Menejment</t>
+          <t>Bugalteriya hisobi</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -19721,12 +19721,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>AD8817586</t>
+          <t>AD4278781</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>52607075280024</t>
+          <t>50210075280013</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -19741,12 +19741,12 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>+998939601100</t>
+          <t>998943239727</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>+998948647848</t>
+          <t>+998914182588</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
@@ -19758,12 +19758,12 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Toxirov Tolibjon Tolibovich</t>
+          <t>Zokirova Feruzabonu</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Bugalteriya hisobi</t>
+          <t>Inson resurslarini boshqarish</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -19778,32 +19778,32 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>AD4278781</t>
+          <t>AD7905276</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>50210075280013</t>
+          <t>60607076610078</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Buxoro viloyati</t>
+          <t>Toshkent shahri</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>Buxoro tumani</t>
+          <t>Sergeli tumani</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>998943239727</t>
+          <t>998774048633</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>+998914182588</t>
+          <t>+998774048633</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
@@ -19815,12 +19815,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Zokirova Feruzabonu</t>
+          <t>Murodova Maxsuna Najmiddin qizi</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Inson resurslarini boshqarish</t>
+          <t>Psixologiya</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -19835,12 +19835,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>AD7905276</t>
+          <t>AD4784304</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>60607076610078</t>
+          <t>61808075720088</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -19850,17 +19850,17 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>Sergeli tumani</t>
+          <t>Chilonzor tumani</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>998774048633</t>
+          <t>998944281822</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>+998774048633</t>
+          <t>+998939278727</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
@@ -19872,7 +19872,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Murodova Maxsuna Najmiddin qizi</t>
+          <t>Muhammadiyeva Dilnoza Sobirovna</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -19892,12 +19892,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>AD4784304</t>
+          <t>AD4164065</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>61808075720088</t>
+          <t>61807076600038</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
@@ -19907,17 +19907,17 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>Chilonzor tumani</t>
+          <t>Mirzo Ulugʻbek tumani</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>998944281822</t>
+          <t>998335153115</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>+998939278727</t>
+          <t>+998333390022</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
@@ -19929,12 +19929,12 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Muhammadiyeva Dilnoza Sobirovna</t>
+          <t>Umaraliyev Zuhriddin Nuriddin ogli</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Psixologiya</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -19949,32 +19949,32 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>AD4164065</t>
+          <t>AD1611400</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>61807076600038</t>
+          <t>50708056910029</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Toshkent shahri</t>
+          <t>Fargona viloyati</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Mirzo Ulugʻbek tumani</t>
+          <t>Bagʻdod tumani</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>998335153115</t>
+          <t>998941899966</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>+998333390022</t>
+          <t>+998941899966</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
@@ -19986,7 +19986,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Umaraliyev Zuhriddin Nuriddin ogli</t>
+          <t>Sayidova Munis Sheraliyevna</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -20006,32 +20006,32 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>AD1611400</t>
+          <t>AD1433274</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>50708056910029</t>
+          <t>00410005590037</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Fargona viloyati</t>
+          <t>Qashqadaryo viloyati</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>Bagʻdod tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>998941899966</t>
+          <t>998908838855</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>+998941899966</t>
+          <t>+998908838855</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
@@ -20043,12 +20043,12 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Sayidova Munis Sheraliyevna</t>
+          <t>Safarova Nilufar Xamidovna</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Ijtimoiy ish</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -20063,32 +20063,32 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>AD1433274</t>
+          <t>AD3628706</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>00410005590037</t>
+          <t>41203128504202</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Qashqadaryo viloyati</t>
+          <t>Buxoro viloyati</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Buxoro tumani</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>998908838855</t>
+          <t>+998939601100</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>+998908838855</t>
+          <t>+998914428652</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
@@ -20100,12 +20100,12 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Safarova Nilufar Xamidovna</t>
+          <t>Itolmasova Maloxat Naimovna</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Ijtimoiy ish</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -20120,12 +20120,12 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>AD3628706</t>
+          <t>AD3695885</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>41203128504202</t>
+          <t>41203872568001</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
@@ -20145,7 +20145,7 @@
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>+998914428652</t>
+          <t>+998975612325</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
@@ -20157,12 +20157,12 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Itolmasova Maloxat Naimovna</t>
+          <t>KOROTAYEVA LYUDMILA GENNADEVNA</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Psixologiya</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -20177,12 +20177,12 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>AD3695885</t>
+          <t>AD4249853</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>41203872568001</t>
+          <t>60802075300027</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
@@ -20197,24 +20197,24 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>+998939601100</t>
+          <t>+998914095252</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>+998975612325</t>
+          <t>+998914058555</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>KOROTAYEVA LYUDMILA GENNADEVNA</t>
+          <t>Najmetdinova Rayxona Jamshedovna</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -20234,12 +20234,12 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>AD4249853</t>
+          <t>AD8253766</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>60802075300027</t>
+          <t>60509075260019</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
@@ -20254,12 +20254,12 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>+998914095252</t>
+          <t>998918331554</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>+998914058555</t>
+          <t>+998918331554</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
@@ -20271,17 +20271,17 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Najmetdinova Rayxona Jamshedovna</t>
+          <t>O'tkurov Javdod Uchkurovich</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Psixologiya</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>O'zbek tili</t>
+          <t>Rus tili</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -20291,32 +20291,32 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>AD8253766</t>
+          <t>AE3501540</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>60509075260019</t>
+          <t>30210986610075</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Buxoro viloyati</t>
+          <t>Toshkent shahri</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>Buxoro tumani</t>
+          <t>Olmazor tumani</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>998918331554</t>
+          <t>998974010133</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>+998918331554</t>
+          <t>+998991220088</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
@@ -20328,17 +20328,17 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>O'tkurov Javdod Uchkurovich</t>
+          <t>Qobilov Malik Muhitdin ogli</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Menejment</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Rus tili</t>
+          <t>O'zbek tili</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -20348,32 +20348,32 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>AE3501540</t>
+          <t>AB4037076</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>30210986610075</t>
+          <t>32104911060018</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Toshkent shahri</t>
+          <t>Buxoro viloyati</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Olmazor tumani</t>
+          <t>Vobkent tumani</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>998974010133</t>
+          <t>998914097878</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>+998991220088</t>
+          <t>+998914097878</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
@@ -20385,7 +20385,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Qobilov Malik Muhitdin ogli</t>
+          <t>Axmatov Farxod Furqatovich</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -20405,12 +20405,12 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>AB4037076</t>
+          <t>AB2768268</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>32104911060018</t>
+          <t>32409985260057</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
@@ -20425,12 +20425,12 @@
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>998914097878</t>
+          <t>+998971462626</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>+998914097878</t>
+          <t>+998980072626</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
@@ -20442,12 +20442,12 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Axmatov Farxod Furqatovich</t>
+          <t>Djumanova Gulnora Mirzaliyevna</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Menejment</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -20462,32 +20462,32 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>AB2768268</t>
+          <t>AD5411751</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>32409985260057</t>
+          <t>43012826860017</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Buxoro viloyati</t>
+          <t>Toshkent viloyati</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Vobkent tumani</t>
+          <t>Chirchiq shahri</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>+998971462626</t>
+          <t>998917760347</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>+998980072626</t>
+          <t>+998917760347</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
@@ -20499,12 +20499,12 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Djumanova Gulnora Mirzaliyevna</t>
+          <t>Qoryogdiyev Elnur Jalil ogli</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Hayot faoliyati xavfsizligi</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -20519,32 +20519,32 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>AD5411751</t>
+          <t>AB6200043</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>43012826860017</t>
+          <t>52403005320020</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Toshkent viloyati</t>
+          <t>Buxoro viloyati</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>Chirchiq shahri</t>
+          <t>Buxoro tumani</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>998917760347</t>
+          <t>998337470909</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>+998917760347</t>
+          <t>+998932902266</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
@@ -20556,7 +20556,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Qoryogdiyev Elnur Jalil ogli</t>
+          <t>Raxmonov Sardorbek Ikrom ogli</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -20576,12 +20576,12 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>AB6200043</t>
+          <t>AE1148018</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>52403005320020</t>
+          <t>31012965320024</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
@@ -20601,7 +20601,7 @@
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>+998932902266</t>
+          <t>+998332700909</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
@@ -20613,12 +20613,12 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Raxmonov Sardorbek Ikrom ogli</t>
+          <t>Murodov Ozodbek Tojiddin ogli</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Hayot faoliyati xavfsizligi</t>
+          <t>Ijtimoiy ish</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -20633,12 +20633,12 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>AE1148018</t>
+          <t>AB5148515</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>31012965320024</t>
+          <t>52004005320012</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
@@ -20648,7 +20648,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Buxoro tumani</t>
+          <t>Qorakoʻl tumani</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -20658,7 +20658,7 @@
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>+998332700909</t>
+          <t>+998337470909</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
@@ -20670,12 +20670,12 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Murodov Ozodbek Tojiddin ogli</t>
+          <t>Ismatov Sardor Sunnatovich</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Ijtimoiy ish</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -20690,12 +20690,12 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>AB5148515</t>
+          <t>AB7035087</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>52004005320012</t>
+          <t>51204015360061</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
@@ -20705,17 +20705,17 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>Qorakoʻl tumani</t>
+          <t>Buxoro tumani</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>998337470909</t>
+          <t>998934501860</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>+998337470909</t>
+          <t>+998944501860</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
@@ -20727,7 +20727,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Ismatov Sardor Sunnatovich</t>
+          <t>Turdiyev Mirjalol Vaxob o'g'li</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -20737,7 +20737,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>O'zbek tili</t>
+          <t>Rus tili</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -20747,32 +20747,32 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>AB7035087</t>
+          <t>AD3840053</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>51204015360061</t>
+          <t>31912933940064</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Buxoro viloyati</t>
+          <t>Toshkent shahri</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>Buxoro tumani</t>
+          <t>Bektemir tumani</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>998934501860</t>
+          <t>+998950208757</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>+998944501860</t>
+          <t>+998900162400</t>
         </is>
       </c>
       <c r="K357" t="inlineStr">
@@ -20784,17 +20784,17 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Turdiyev Mirjalol Vaxob o'g'li</t>
+          <t>Egamberdiyeva Sarvinoz Shavkatovna</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Inson resurslarini boshqarish</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Rus tili</t>
+          <t>O'zbek tili</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -20804,12 +20804,12 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>AD3840053</t>
+          <t>AD8881372</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>31912933940064</t>
+          <t>61204086620010</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
@@ -20819,34 +20819,34 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>Bektemir tumani</t>
+          <t>Mirzo Ulugʻbek tumani</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>+998950208757</t>
+          <t>998935236622</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>+998900162400</t>
+          <t>+998946201474</t>
         </is>
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Egamberdiyeva Sarvinoz Shavkatovna</t>
+          <t>Salimov Mamurjon Iskandarovich</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Inson resurslarini boshqarish</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -20861,32 +20861,32 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>AD8881372</t>
+          <t>AD1925742</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>61204086620010</t>
+          <t>52809066150019</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Toshkent shahri</t>
+          <t>Samarqand viloyati</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>Mirzo Ulugʻbek tumani</t>
+          <t>Toyloq tumani</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>998935236622</t>
+          <t>998886158603</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>+998946201474</t>
+          <t>+998886158603</t>
         </is>
       </c>
       <c r="K359" t="inlineStr">
@@ -20898,12 +20898,12 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Salimov Mamurjon Iskandarovich</t>
+          <t>Bayzaqov Mirmuhsin Rasuljon ogli</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Metrologiya va standartlashtirish</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -20918,32 +20918,32 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>AD1925742</t>
+          <t>AD8882474</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>52809066150019</t>
+          <t>50302086450052</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Samarqand viloyati</t>
+          <t>Sirdaryo viloyati</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>Toyloq tumani</t>
+          <t>Guliston tumani</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>998886158603</t>
+          <t>998700177208</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>+998886158603</t>
+          <t>+998994420382</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
@@ -20955,12 +20955,12 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Bayzaqov Mirmuhsin Rasuljon ogli</t>
+          <t>Ulugbekov Sardor Ulugbek ogli</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Metrologiya va standartlashtirish</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -20975,32 +20975,32 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>AD8882474</t>
+          <t>AD9943736</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>50302086450052</t>
+          <t>51103070005071</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Sirdaryo viloyati</t>
+          <t>Toshkent shahri</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>Guliston tumani</t>
+          <t>Mirzo Ulugʻbek tumani</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>998700177208</t>
+          <t>998938290504</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>+998994420382</t>
+          <t>+998953342332</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
@@ -21012,7 +21012,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Ulugbekov Sardor Ulugbek ogli</t>
+          <t>Tursunboyeva Ziyoda Xamid qizi</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -21032,12 +21032,12 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>AD9943736</t>
+          <t>AD4317736</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>51103070005071</t>
+          <t>60107076620018</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
@@ -21052,12 +21052,12 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>998938290504</t>
+          <t>998908147557</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>+998953342332</t>
+          <t>+998908147557</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
@@ -21069,12 +21069,12 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Tursunboyeva Ziyoda Xamid qizi</t>
+          <t>SAMANDAROVA SOGDIANA MUHIDDIN QIZI</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Psixologiya</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -21089,32 +21089,32 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>AD4317736</t>
+          <t>AE2177737</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>60107076620018</t>
+          <t>60802075300027</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Toshkent shahri</t>
+          <t>Buxoro viloyati</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Mirzo Ulugʻbek tumani</t>
+          <t>Buxoro tumani</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>998908147557</t>
+          <t>+998904140403</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>+998908147557</t>
+          <t>+998914058555</t>
         </is>
       </c>
       <c r="K363" t="inlineStr">
@@ -21126,12 +21126,12 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>SAMANDAROVA SOGDIANA MUHIDDIN QIZI</t>
+          <t>Boynazarova Hosila</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Psixologiya</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -21146,32 +21146,32 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>AE2177737</t>
+          <t>AD2026343</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>60802075300027</t>
+          <t>60806065730010</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Buxoro viloyati</t>
+          <t>Qashqadaryo viloyati</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>Buxoro tumani</t>
+          <t>Yakkabogʻ tumani</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>+998904140403</t>
+          <t>998902445506</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>+998914058555</t>
+          <t>+998974510506</t>
         </is>
       </c>
       <c r="K364" t="inlineStr">
@@ -21183,12 +21183,12 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Boynazarova Hosila</t>
+          <t>RAXMONOV XURSHIDBEK NODIROVICH</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Hayot faoliyati xavfsizligi</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -21203,32 +21203,32 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>AD2026343</t>
+          <t>AD4158952</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>60806065730010</t>
+          <t>41212945896574</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Qashqadaryo viloyati</t>
+          <t>Buxoro viloyati</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>Yakkabogʻ tumani</t>
+          <t>Kogon tumani</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>998902445506</t>
+          <t>+998914095252</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>+998974510506</t>
+          <t>+998936262286</t>
         </is>
       </c>
       <c r="K365" t="inlineStr">
@@ -21240,12 +21240,12 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>RAXMONOV XURSHIDBEK NODIROVICH</t>
+          <t>ELMURODOV OZODBEK OTABEKOVICH</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Hayot faoliyati xavfsizligi</t>
+          <t>Bugalteriya hisobi</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -21260,12 +21260,12 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>AD4158952</t>
+          <t>AD4105390</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>41212945896574</t>
+          <t>31506985680412</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
@@ -21285,7 +21285,7 @@
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>+998936262286</t>
+          <t>+998995257645</t>
         </is>
       </c>
       <c r="K366" t="inlineStr">
@@ -21297,12 +21297,12 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>ELMURODOV OZODBEK OTABEKOVICH</t>
+          <t>TUXTAYEVA AMINABONU QAHRAMON QIZI</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Bugalteriya hisobi</t>
+          <t>Psixologiya</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -21317,12 +21317,12 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>AD4105390</t>
+          <t>AB8254776</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>31506985680412</t>
+          <t>41312941000013</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
@@ -21332,7 +21332,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>Kogon tumani</t>
+          <t>Buxoro tumani</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -21342,7 +21342,7 @@
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>+998995257645</t>
+          <t>+998934630600</t>
         </is>
       </c>
       <c r="K367" t="inlineStr">
@@ -21354,12 +21354,12 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>TUXTAYEVA AMINABONU QAHRAMON QIZI</t>
+          <t>PO'LOTOV ISTAM RAMAZONOVICH</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Psixologiya</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -21374,12 +21374,12 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>AB8254776</t>
+          <t>AE3149883</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>41312941000013</t>
+          <t>31807925280016</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
@@ -21399,7 +21399,7 @@
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>+998934630600</t>
+          <t>+998945490605</t>
         </is>
       </c>
       <c r="K368" t="inlineStr">
@@ -21411,12 +21411,12 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>PO'LOTOV ISTAM RAMAZONOVICH</t>
+          <t>Quvvatova Ruxshona</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Psixologiya</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -21431,32 +21431,32 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>AE3149883</t>
+          <t>AD9049048</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>31807925280016</t>
+          <t>61412076790016</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Buxoro viloyati</t>
+          <t>Toshkent viloyati</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Buxoro tumani</t>
+          <t>Piskent tumani</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>+998914095252</t>
+          <t>998950592978</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>+998945490605</t>
+          <t>+998950741214</t>
         </is>
       </c>
       <c r="K369" t="inlineStr">
@@ -21468,17 +21468,17 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Quvvatova Ruxshona</t>
+          <t>Trofimova Evelina Vladimirovna</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Psixologiya</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>O'zbek tili</t>
+          <t>Rus tili</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -21488,44 +21488,44 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>AD9049048</t>
+          <t>AD3695493</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>61412076790016</t>
+          <t>61706076590036</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Toshkent viloyati</t>
+          <t>Toshkent shahri</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>Piskent tumani</t>
+          <t>Uchtepa tumani</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>998950592978</t>
+          <t>998903217238</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>+998950741214</t>
+          <t>+998990644666</t>
         </is>
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Trofimova Evelina Vladimirovna</t>
+          <t>Xusanboyev Mirjalol Baxodir ogli</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -21535,7 +21535,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Rus tili</t>
+          <t>O'zbek tili</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -21545,32 +21545,32 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>AD3695493</t>
+          <t>AD4655876</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>61706076590036</t>
+          <t>52003076780017</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Toshkent shahri</t>
+          <t>Toshkent viloyati</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>Uchtepa tumani</t>
+          <t>Qibray tumani</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>998903217238</t>
+          <t>998974041076</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>+998990644666</t>
+          <t>+998880780320</t>
         </is>
       </c>
       <c r="K371" t="inlineStr">
@@ -21582,7 +21582,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Xusanboyev Mirjalol Baxodir ogli</t>
+          <t>Ergashev Shohjaxon</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -21602,32 +21602,32 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>AD4655876</t>
+          <t>AD5186284</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>52003076780017</t>
+          <t>52406075740071</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Toshkent viloyati</t>
+          <t>Qashqadaryo viloyati</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Qibray tumani</t>
+          <t>Qarshi tumani</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>998974041076</t>
+          <t>998914697007</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>+998880780320</t>
+          <t>+998900837017</t>
         </is>
       </c>
       <c r="K372" t="inlineStr">
@@ -21639,12 +21639,12 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Ergashev Shohjaxon</t>
+          <t>Kamolov Shoxboz Baxtiyor ogli</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Ijtimoiy ish</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -21659,32 +21659,32 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>AD5186284</t>
+          <t>AD7842133</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>52406075740071</t>
+          <t>51611076790025</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Qashqadaryo viloyati</t>
+          <t>Toshkent viloyati</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>Qarshi tumani</t>
+          <t>Piskent tumani</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>998914697007</t>
+          <t>998887311611</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>+998900837017</t>
+          <t>+998887311611</t>
         </is>
       </c>
       <c r="K373" t="inlineStr">
@@ -21696,12 +21696,12 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Kamolov Shoxboz Baxtiyor ogli</t>
+          <t>Salimov Jahongir Samad ogli</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Ijtimoiy ish</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -21716,32 +21716,32 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>AD7842133</t>
+          <t>AD9447133</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>51611076790025</t>
+          <t>50110075290040</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Toshkent viloyati</t>
+          <t>Buxoro viloyati</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>Piskent tumani</t>
+          <t>Vobkent tumani</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>998887311611</t>
+          <t>998990788664</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>+998887311611</t>
+          <t>+998502422040</t>
         </is>
       </c>
       <c r="K374" t="inlineStr">
@@ -21753,12 +21753,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Salimov Jahongir Samad ogli</t>
+          <t>Rajabova Sevinch Anvar qizi</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Psixologiya</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -21773,12 +21773,12 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>AD9447133</t>
+          <t>AD9047497</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>50110075290040</t>
+          <t>62212075780031</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
@@ -21788,17 +21788,17 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>Vobkent tumani</t>
+          <t>Kogon tumani</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>998990788664</t>
+          <t>998991255019</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>+998502422040</t>
+          <t>+998503015040</t>
         </is>
       </c>
       <c r="K375" t="inlineStr">
@@ -21810,12 +21810,12 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Rajabova Sevinch Anvar qizi</t>
+          <t>Sayfuddinov Dalerbek  Doniyorovich</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Psixologiya</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -21830,12 +21830,12 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>AD9047497</t>
+          <t>AD5281217</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>62212075780031</t>
+          <t>52711075380049</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
@@ -21855,7 +21855,7 @@
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>+998503015040</t>
+          <t>+998991255019</t>
         </is>
       </c>
       <c r="K376" t="inlineStr">
@@ -21867,12 +21867,12 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Sayfuddinov Dalerbek  Doniyorovich</t>
+          <t>Xumoyun Orifjonov Ortiqboy ovich</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Mehnat muhofazasi va texnika xavfsizligi</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -21887,32 +21887,32 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>AD5281217</t>
+          <t>AD3790938</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>52711075380049</t>
+          <t>52204076790019</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Buxoro viloyati</t>
+          <t>Toshkent viloyati</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>Kogon tumani</t>
+          <t>Olmaliq shahri</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>998991255019</t>
+          <t>998936219621</t>
         </is>
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>+998991255019</t>
+          <t>+998936219621</t>
         </is>
       </c>
       <c r="K377" t="inlineStr">
@@ -21924,12 +21924,12 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Xumoyun Orifjonov Ortiqboy ovich</t>
+          <t>Nizomiddinova Munavvar Ilxom qizi</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Mehnat muhofazasi va texnika xavfsizligi</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -21944,49 +21944,49 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>AD3790938</t>
+          <t>AD7603396</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>52204076790019</t>
+          <t>60106066100033</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Toshkent viloyati</t>
+          <t>Samarqand viloyati</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>Olmaliq shahri</t>
+          <t>Paxtachi tumani</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>998936219621</t>
+          <t>998939522203</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>+998936219621</t>
+          <t>+998939522203</t>
         </is>
       </c>
       <c r="K378" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-16</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Nizomiddinova Munavvar Ilxom qizi</t>
+          <t>Mastonov Shamshod Mansur o'g'li</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Bugalteriya hisobi</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -22001,32 +22001,32 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>AD7603396</t>
+          <t>AB1962400</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>60106066100033</t>
+          <t>32304961050025</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Samarqand viloyati</t>
+          <t>Buxoro viloyati</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>Paxtachi tumani</t>
+          <t>Buxoro tumani</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>998939522203</t>
+          <t>998914041013</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>+998939522203</t>
+          <t>+998995899981</t>
         </is>
       </c>
       <c r="K379" t="inlineStr">
@@ -22038,12 +22038,12 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Mastonov Shamshod Mansur o'g'li</t>
+          <t>Axrorov Sarvar Anvarivich</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Bugalteriya hisobi</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -22058,32 +22058,32 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>AB1962400</t>
+          <t>AD6794891</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>32304961050025</t>
+          <t>51408076130043</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Buxoro viloyati</t>
+          <t>Samarqand viloyati</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>Buxoro tumani</t>
+          <t>Urgut tumani</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>998914041013</t>
+          <t>998904640232</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>+998995899981</t>
+          <t>+998904640232</t>
         </is>
       </c>
       <c r="K380" t="inlineStr">
@@ -22095,7 +22095,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Axrorov Sarvar Anvarivich</t>
+          <t>Saloxitdinova Durdona Sur'atjon qizi</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -22115,12 +22115,12 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>AD6794891</t>
+          <t>AD7978684</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>51408076130043</t>
+          <t>60410076130088</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
@@ -22135,24 +22135,24 @@
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>998904640232</t>
+          <t>998902710233</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>+998904640232</t>
+          <t>+998952733407</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
+          <t>2025-08-17</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Saloxitdinova Durdona Sur'atjon qizi</t>
+          <t>Arabboyev Javlonbek</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -22172,32 +22172,32 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>AD7978684</t>
+          <t>AD1846631</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>60410076130088</t>
+          <t>50707055880076</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Samarqand viloyati</t>
+          <t>Namangan viloyati</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>Urgut tumani</t>
+          <t>Namangan tumani</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>998902710233</t>
+          <t>998936672524</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>+998952733407</t>
+          <t>+998936672524</t>
         </is>
       </c>
       <c r="K382" t="inlineStr">
@@ -22209,7 +22209,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Arabboyev Javlonbek</t>
+          <t>Obidov Sarvarbek Sadriddin ogli</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -22229,49 +22229,49 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>AD1846631</t>
+          <t>AD8610812</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>50707055880076</t>
+          <t>51308075310061</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Namangan viloyati</t>
+          <t>Buxoro viloyati</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>Namangan tumani</t>
+          <t>Gʻijduvon tumani</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>998936672524</t>
+          <t>998931759619</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>+998936672524</t>
+          <t>+998907315567</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Obidov Sarvarbek Sadriddin ogli</t>
+          <t>Yusupov Odilbek Oybek ogli</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Bugalteriya hisobi</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -22286,32 +22286,32 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>AD8610812</t>
+          <t>AD3433993</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>51308075310061</t>
+          <t>52104076520024</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Buxoro viloyati</t>
+          <t>Toshkent shahri</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>Gʻijduvon tumani</t>
+          <t>Yunusobod tumani</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>998931759619</t>
+          <t>998900531581</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>+998907315567</t>
+          <t>+998903221581</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
@@ -22323,12 +22323,12 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Yusupov Odilbek Oybek ogli</t>
+          <t>Masharifov masharif murod ogli</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Bugalteriya hisobi</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -22343,32 +22343,32 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>AD3433993</t>
+          <t>AD4081861</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>52104076520024</t>
+          <t>51212057130018</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Toshkent shahri</t>
+          <t>Xorazm viloyati</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>Yunusobod tumani</t>
+          <t>Urganch tumani</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>998900531581</t>
+          <t>998200056838</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>+998903221581</t>
+          <t>+998918686838</t>
         </is>
       </c>
       <c r="K385" t="inlineStr">
@@ -22380,12 +22380,12 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Masharifov masharif murod ogli</t>
+          <t>Sharipova Shaxnoza Ravshan kizi</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Inson resurslarini boshqarish</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -22400,32 +22400,32 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>AD4081861</t>
+          <t>AD7979208</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>51212057130018</t>
+          <t>63009076590027</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Xorazm viloyati</t>
+          <t>Toshkent shahri</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Urganch tumani</t>
+          <t>Yangihayot tumani</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>998200056838</t>
+          <t>+998977309054</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>+998918686838</t>
+          <t>+998977309054</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
@@ -22437,12 +22437,12 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Sharipova Shaxnoza Ravshan kizi</t>
+          <t>Teshaeva zulfizarbonu</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Inson resurslarini boshqarish</t>
+          <t>Bugalteriya hisobi</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -22457,12 +22457,12 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>AD7979208</t>
+          <t>AC0437935</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>63009076590027</t>
+          <t>41202659003002</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
@@ -22472,17 +22472,17 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Yangihayot tumani</t>
+          <t>Chilonzor tumani</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>+998977309054</t>
+          <t>998934258101</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>+998977309054</t>
+          <t>+998979004444</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
@@ -22494,12 +22494,12 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Teshaeva zulfizarbonu</t>
+          <t>Teshayeva Aminabonu Baxtiyorovna</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Bugalteriya hisobi</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -22514,12 +22514,12 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>AC0437935</t>
+          <t>AD6502161</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>41202659003002</t>
+          <t>62412075260072</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
@@ -22534,12 +22534,12 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>998934258101</t>
+          <t>998880063663</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>+998979004444</t>
+          <t>+998880063663</t>
         </is>
       </c>
       <c r="K388" t="inlineStr">
@@ -22551,7 +22551,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Teshayeva Aminabonu Baxtiyorovna</t>
+          <t>Imamov Aydar Damirovich</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -22561,7 +22561,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>O'zbek tili</t>
+          <t>Rus tili</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -22571,12 +22571,12 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>AD6502161</t>
+          <t>AD4738493</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>62412075260072</t>
+          <t>50609076750139</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
@@ -22586,17 +22586,17 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>Chilonzor tumani</t>
+          <t>Olmazor tumani</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>998880063663</t>
+          <t>998770788957</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>+998880063663</t>
+          <t>+998330080844</t>
         </is>
       </c>
       <c r="K389" t="inlineStr">
@@ -22608,7 +22608,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Imamov Aydar Damirovich</t>
+          <t>Obidov Asilbek Tohir ogli</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -22618,7 +22618,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Rus tili</t>
+          <t>O'zbek tili</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -22628,32 +22628,32 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>AD4738493</t>
+          <t>AD0986511</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>50609076750139</t>
+          <t>50812056810066</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Toshkent shahri</t>
+          <t>Toshkent viloyati</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>Olmazor tumani</t>
+          <t>Chinoz tumani</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>998770788957</t>
+          <t>998888744144</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>+998330080844</t>
+          <t>+998901193090</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
@@ -22665,7 +22665,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Obidov Asilbek Tohir ogli</t>
+          <t>Fozilova Saodat Soxib Qizi</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -22685,32 +22685,32 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>AD0986511</t>
+          <t>AD7623885</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>50812056810066</t>
+          <t>60402075540023</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Toshkent viloyati</t>
+          <t>Jizzax viloyati</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>Chinoz tumani</t>
+          <t>Jizzax shahri</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>998888744144</t>
+          <t>998974402178</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>+998901193090</t>
+          <t>+998902977782</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
@@ -22722,52 +22722,37 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Fozilova Saodat Soxib Qizi</t>
-        </is>
-      </c>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>Yurisprudensiya</t>
-        </is>
-      </c>
-      <c r="C392" t="inlineStr">
-        <is>
-          <t>O'zbek tili</t>
-        </is>
-      </c>
-      <c r="D392" t="inlineStr">
-        <is>
-          <t>Kunduzgi</t>
+          <t>Temur Xodjiyev</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>AD7623885</t>
+          <t>AD5613988</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>60402075540023</t>
+          <t>52411076730031</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>Jizzax viloyati</t>
+          <t>Toshkent viloyati</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Jizzax shahri</t>
+          <t>Piskent tumani</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>998974402178</t>
+          <t>998956600737</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>+998902977782</t>
+          <t>+998999433004</t>
         </is>
       </c>
       <c r="K392" t="inlineStr">
@@ -22779,49 +22764,64 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Temur Xodjiyev</t>
+          <t>Furqatov Marufjon Farrux ogli</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>AD5613988</t>
+          <t>AD4264388</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>52411076730031</t>
+          <t>50908076520035</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>Toshkent viloyati</t>
+          <t>Toshkent shahri</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>Piskent tumani</t>
+          <t>Yunusobod tumani</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>998956600737</t>
+          <t>998998478934</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>+998999433004</t>
+          <t>+998994816220</t>
         </is>
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Furqatov Marufjon Farrux ogli</t>
+          <t>Baxodirova Shirin Anvarjonovna</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -22831,7 +22831,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>O'zbek tili</t>
+          <t>Rus tili</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -22841,32 +22841,32 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>AD4264388</t>
+          <t>AD7805267</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>50908076520035</t>
+          <t>60805086180082</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>Toshkent shahri</t>
+          <t>Samarqand viloyati</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>Yunusobod tumani</t>
+          <t>Samarqand shahri</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>998998478934</t>
+          <t>998904590939</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>+998994816220</t>
+          <t>+998906044979</t>
         </is>
       </c>
       <c r="K394" t="inlineStr">
@@ -22878,17 +22878,17 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Baxodirova Shirin Anvarjonovna</t>
+          <t>Abdulxakimov Jafarali Odil ogli</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Metrologiya va standartlashtirish</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Rus tili</t>
+          <t>O'zbek tili</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -22898,32 +22898,32 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>AD7805267</t>
+          <t>AD7373831</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>60805086180082</t>
+          <t>50511076360071</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>Samarqand viloyati</t>
+          <t>Sirdaryo viloyati</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>Samarqand shahri</t>
+          <t>Sirdaryo tumani</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>998904590939</t>
+          <t>998772352299</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>+998906044979</t>
+          <t>+998993098129</t>
         </is>
       </c>
       <c r="K395" t="inlineStr">
@@ -22935,12 +22935,12 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Abdulxakimov Jafarali Odil ogli</t>
+          <t>Mingboyeva Nurxon Araboy qizi</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Metrologiya va standartlashtirish</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -22955,32 +22955,32 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>AD7373831</t>
+          <t>AD2160047</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>50511076360071</t>
+          <t>61503057010019</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>Sirdaryo viloyati</t>
+          <t>Fargona viloyati</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>Sirdaryo tumani</t>
+          <t>Fargʻona tumani</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>998772352299</t>
+          <t>998904088779</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>+998993098129</t>
+          <t>+998885970315</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
@@ -22992,7 +22992,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Mingboyeva Nurxon Araboy qizi</t>
+          <t>Habibullayev Hojiakbar Ismoiljon ogli</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -23012,12 +23012,12 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>AD2160047</t>
+          <t>AD6684301</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>61503057010019</t>
+          <t>51403076960085</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
@@ -23027,17 +23027,17 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>Fargʻona tumani</t>
+          <t>Rishton tumani</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>998904088779</t>
+          <t>998905351403</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>+998885970315</t>
+          <t>+998905351403</t>
         </is>
       </c>
       <c r="K397" t="inlineStr">
@@ -23049,12 +23049,12 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Habibullayev Hojiakbar Ismoiljon ogli</t>
+          <t>Hayitmurodov Ozodbek</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Mehnat muhofazasi va texnika xavfsizligi</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -23069,32 +23069,32 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>AD6684301</t>
+          <t>AD8186923</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>51403076960085</t>
+          <t>52511076450026</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Fargona viloyati</t>
+          <t>Sirdaryo viloyati</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>Rishton tumani</t>
+          <t>Guliston shahri</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>998905351403</t>
+          <t>998883072268</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>+998905351403</t>
+          <t>+998933221422</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
@@ -23106,12 +23106,12 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Hayitmurodov Ozodbek</t>
+          <t>Xudayberdiyeva Ruxshona Akmal kizi</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Mehnat muhofazasi va texnika xavfsizligi</t>
+          <t>Bugalteriya hisobi</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -23126,32 +23126,32 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>AD8186923</t>
+          <t>AD5529909</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>52511076450026</t>
+          <t>62412076860033</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>Sirdaryo viloyati</t>
+          <t>Toshkent shahri</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>Guliston shahri</t>
+          <t>Mirzo Ulugʻbek tumani</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>998883072268</t>
+          <t>998959770879</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>+998933221422</t>
+          <t>+998901369009</t>
         </is>
       </c>
       <c r="K399" t="inlineStr">
@@ -23163,12 +23163,12 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Xudayberdiyeva Ruxshona Akmal kizi</t>
+          <t>Atabayev Umarbek Umirbekovich</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Bugalteriya hisobi</t>
+          <t>Mehnat muhofazasi va texnika xavfsizligi</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -23183,32 +23183,32 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>AD5529909</t>
+          <t>AD5294160</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>62412076860033</t>
+          <t>52109077190034</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>Toshkent shahri</t>
+          <t>Xorazm viloyati</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>Mirzo Ulugʻbek tumani</t>
+          <t>Urganch shahri</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>998959770879</t>
+          <t>998998657077</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>+998901369009</t>
+          <t>+998974515101</t>
         </is>
       </c>
       <c r="K400" t="inlineStr">
@@ -23220,12 +23220,12 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Atabayev Umarbek Umirbekovich</t>
+          <t>Abdujabborov Shabozjon Sherzodjon ogli</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Mehnat muhofazasi va texnika xavfsizligi</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -23240,32 +23240,32 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>AD5294160</t>
+          <t>AD2906456</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>52109077190034</t>
+          <t>52201066960045</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>Xorazm viloyati</t>
+          <t>Fargona viloyati</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>Urganch shahri</t>
+          <t>Rishton tumani</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>998998657077</t>
+          <t>998200100622</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>+998974515101</t>
+          <t>+998999872201</t>
         </is>
       </c>
       <c r="K401" t="inlineStr">
@@ -23277,7 +23277,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Abdujabborov Shabozjon Sherzodjon ogli</t>
+          <t>Abdumajidov Abdulaziz</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -23287,7 +23287,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>O'zbek tili</t>
+          <t>Rus tili</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -23297,32 +23297,32 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>AD2906456</t>
+          <t>AD7002000</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>52201066960045</t>
+          <t>51311076610018</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>Fargona viloyati</t>
+          <t>Toshkent shahri</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>Rishton tumani</t>
+          <t>Olmazor tumani</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>998200100622</t>
+          <t>998977072250</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>+998999872201</t>
+          <t>+998977072250</t>
         </is>
       </c>
       <c r="K402" t="inlineStr">
@@ -23334,7 +23334,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Abdumajidov Abdulaziz</t>
+          <t>Tolibjanov Ibrohim</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -23344,7 +23344,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Rus tili</t>
+          <t>O'zbek tili</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -23354,44 +23354,44 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>AD7002000</t>
+          <t>AD5415716</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>51311076610018</t>
+          <t>52608075890082</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>Toshkent shahri</t>
+          <t>Namangan viloyati</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>Olmazor tumani</t>
+          <t>Chortoq tumani</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>998977072250</t>
+          <t>998770052429</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>+998977072250</t>
+          <t>+998770052429</t>
         </is>
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Tolibjanov Ibrohim</t>
+          <t>Eshmatov Umidjon Gayrat ogli</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -23401,7 +23401,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>O'zbek tili</t>
+          <t>Rus tili</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -23411,32 +23411,32 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>AD5415716</t>
+          <t>AD1992857</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>52608075890082</t>
+          <t>50407055540089</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>Namangan viloyati</t>
+          <t>Jizzax viloyati</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>Chortoq tumani</t>
+          <t>Jizzax shahri</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>998770052429</t>
+          <t>998938382211</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>+998770052429</t>
+          <t>+998932534353</t>
         </is>
       </c>
       <c r="K404" t="inlineStr">
@@ -23448,7 +23448,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Eshmatov Umidjon Gayrat ogli</t>
+          <t>Azimkulova Gulsanam Azizjon qizi</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -23458,7 +23458,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Rus tili</t>
+          <t>O'zbek tili</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -23468,32 +23468,32 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>AD1992857</t>
+          <t>AD6613276</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>50407055540089</t>
+          <t>62502086030035</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>Jizzax viloyati</t>
+          <t>Samarqand viloyati</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>Jizzax shahri</t>
+          <t>Bulungʻur tumani</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>998938382211</t>
+          <t>+998993685582</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>+998932534353</t>
+          <t>+998772202508</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
@@ -23505,7 +23505,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Azimkulova Gulsanam Azizjon qizi</t>
+          <t>Hakimjonova Shukrona Bexzod qizi</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -23525,32 +23525,32 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>AD6613276</t>
+          <t>AD7665799</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>62502086030035</t>
+          <t>62306075590070</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>Samarqand viloyati</t>
+          <t>Qashqadaryo viloyati</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>Bulungʻur tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>+998993685582</t>
+          <t>998885892999</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>+998772202508</t>
+          <t>+998885892999</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
@@ -23562,7 +23562,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Hakimjonova Shukrona Bexzod qizi</t>
+          <t>Boysinova Sohila Baxodir qizi</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -23582,12 +23582,12 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>AD7665799</t>
+          <t>AD4773927</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>62306075590070</t>
+          <t>61008065590073</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
@@ -23602,12 +23602,12 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>998885892999</t>
+          <t>998770627806</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>+998885892999</t>
+          <t>+998770627806</t>
         </is>
       </c>
       <c r="K407" t="inlineStr">
@@ -23619,7 +23619,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Boysinova Sohila Baxodir qizi</t>
+          <t>Umidjon Nazarov</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -23639,44 +23639,44 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>AD4773927</t>
+          <t>AB1578484</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>61008065590073</t>
+          <t>12345678901234</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>Qashqadaryo viloyati</t>
+          <t>Samarqand viloyati</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Urgut tumani</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>998770627806</t>
+          <t>998883741188</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>+998770627806</t>
+          <t>+998772773765</t>
         </is>
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Umidjon Nazarov</t>
+          <t>Choriyev Farahmed Nuraliyevich</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -23696,32 +23696,32 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>AB1578484</t>
+          <t>AD6146769</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>12345678901234</t>
+          <t>50602076230139</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>Samarqand viloyati</t>
+          <t>Toshkent shahri</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>Urgut tumani</t>
+          <t>Mirzo Ulugʻbek tumani</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>998883741188</t>
+          <t>998770268004</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>+998772773765</t>
+          <t>+998975334412</t>
         </is>
       </c>
       <c r="K409" t="inlineStr">
@@ -23733,7 +23733,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Choriyev Farahmed Nuraliyevich</t>
+          <t>ARTKOVA NARGIZA RUSTAMOVNA</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -23753,32 +23753,32 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>AD6146769</t>
+          <t>AD1811796</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>50602076230139</t>
+          <t>41705941140019</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>Toshkent shahri</t>
+          <t>Buxoro viloyati</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>Mirzo Ulugʻbek tumani</t>
+          <t>Kogon tumani</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>998770268004</t>
+          <t>+998914095252</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>+998975334412</t>
+          <t>+998772650560</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
@@ -23790,12 +23790,12 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>ARTKOVA NARGIZA RUSTAMOVNA</t>
+          <t>Muhammadov Muhammadali Umidovich</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Ijtimoiy ish</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -23810,12 +23810,12 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>AD1811796</t>
+          <t>AD3797714</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>41705941140019</t>
+          <t>51506075350058</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
@@ -23825,17 +23825,17 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Kogon tumani</t>
+          <t>Jondor tumani</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>+998914095252</t>
+          <t>998907885527</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>+998772650560</t>
+          <t>+998950305527</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
@@ -23847,12 +23847,12 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Muhammadov Muhammadali Umidovich</t>
+          <t>Jumanuyozova Muxayyo Maqsudovna</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Ijtimoiy ish</t>
+          <t>Hayot faoliyati xavfsizligi</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -23867,32 +23867,32 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>AD3797714</t>
+          <t>AB5890595</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>51506075350058</t>
+          <t>42908843180054</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>Buxoro viloyati</t>
+          <t>Xorazm viloyati</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>Jondor tumani</t>
+          <t>Xiva shahri</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>998907885527</t>
+          <t>998992539090</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>+998950305527</t>
+          <t>+998996631116</t>
         </is>
       </c>
       <c r="K412" t="inlineStr">
@@ -23904,7 +23904,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Jumanuyozova Muxayyo Maqsudovna</t>
+          <t>JUMANIYOZOVA MUXAYYO MAQSUDOVNA</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -23924,7 +23924,7 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>AB5890595</t>
+          <t>AB5890898</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
@@ -23961,12 +23961,12 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>JUMANIYOZOVA MUXAYYO MAQSUDOVNA</t>
+          <t>Berdiyev Adxam</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Hayot faoliyati xavfsizligi</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -23981,32 +23981,32 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>AB5890898</t>
+          <t>AD4482419</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>42908843180054</t>
+          <t>51903076330021</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>Xorazm viloyati</t>
+          <t>Surxondaryo viloyati</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>Xiva shahri</t>
+          <t>Uzun tumani</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>998992539090</t>
+          <t>998501070251</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>+998996631116</t>
+          <t>+998501070251</t>
         </is>
       </c>
       <c r="K414" t="inlineStr">
@@ -24018,7 +24018,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Berdiyev Adxam</t>
+          <t>SARKAYEVA FARIZA</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -24038,32 +24038,32 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>AD4482419</t>
+          <t>AB3309162</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>51903076330021</t>
+          <t>41409842890029</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>Surxondaryo viloyati</t>
+          <t>Sirdaryo viloyati</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>Uzun tumani</t>
+          <t>Guliston shahri</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>998501070251</t>
+          <t>998972467884</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>+998501070251</t>
+          <t>+998972467884</t>
         </is>
       </c>
       <c r="K415" t="inlineStr">
@@ -24075,7 +24075,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>SARKAYEVA FARIZA</t>
+          <t>Sheraliyeva Hilola</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -24095,12 +24095,12 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>AB3309162</t>
+          <t>AD9232572</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>41409842890029</t>
+          <t>61207076450035</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
@@ -24132,7 +24132,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Sheraliyeva Hilola</t>
+          <t>Samiyev Ozodbek</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -24152,32 +24152,32 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>AD9232572</t>
+          <t>AD1497277</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>61207076450035</t>
+          <t>53003076930055</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>Sirdaryo viloyati</t>
+          <t>Fargona viloyati</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>Guliston shahri</t>
+          <t>Beshariq tumani</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>998972467884</t>
+          <t>998944412863</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>+998972467884</t>
+          <t>+998930457444</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
@@ -24189,7 +24189,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Samiyev Ozodbek</t>
+          <t>Sheraliyev Ogabek</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -24209,12 +24209,12 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>AD1497277</t>
+          <t>AE2314671</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>53003076930055</t>
+          <t>52210086930059</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
@@ -24229,7 +24229,7 @@
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>998944412863</t>
+          <t>998958707444</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
@@ -24246,7 +24246,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Sheraliyev Ogabek</t>
+          <t>Bozorova Xolida Xakimovna</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -24266,49 +24266,49 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>AE2314671</t>
+          <t>AE1488654</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>52210086930059</t>
+          <t>40110822680020</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>Fargona viloyati</t>
+          <t>Qashqadaryo viloyati</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>Beshariq tumani</t>
+          <t>Kasbi tumani</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>998958707444</t>
+          <t>998945360110</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>+998930457444</t>
+          <t>+998949800110</t>
         </is>
       </c>
       <c r="K419" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Bozorova Xolida Xakimovna</t>
+          <t>Tillabayeva Sevara Xolmatovna</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Psixologiya</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -24323,32 +24323,32 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>AE1488654</t>
+          <t>AC1619766</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>40110822680020</t>
+          <t>41011886610013</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>Qashqadaryo viloyati</t>
+          <t>Toshkent shahri</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>Kasbi tumani</t>
+          <t>Olmazor tumani</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>998945360110</t>
+          <t>998977472890</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>+998949800110</t>
+          <t>+998977472980</t>
         </is>
       </c>
       <c r="K420" t="inlineStr">
@@ -24360,12 +24360,12 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Tillabayeva Sevara Xolmatovna</t>
+          <t>Olimov Xosilbek G'ofurjonovich</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Psixologiya</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -24380,32 +24380,32 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>AC1619766</t>
+          <t>AD0181107</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>41011886610013</t>
+          <t>52203056430024</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>Toshkent shahri</t>
+          <t>Sirdaryo viloyati</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>Olmazor tumani</t>
+          <t>Mirzaobod tumani</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>998977472890</t>
+          <t>998959502203</t>
         </is>
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>+998977472980</t>
+          <t>+998959502203</t>
         </is>
       </c>
       <c r="K421" t="inlineStr">
@@ -24417,12 +24417,12 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Olimov Xosilbek G'ofurjonovich</t>
+          <t>Nazarov SHuhratbek Sherzod ogli</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Inson resurslarini boshqarish</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -24437,32 +24437,32 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>AD0181107</t>
+          <t>AD9259094</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>52203056430024</t>
+          <t>51506085180054</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>Sirdaryo viloyati</t>
+          <t>Andijon viloyati</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>Mirzaobod tumani</t>
+          <t>Shahrixon tuman</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>998959502203</t>
+          <t>998951200052</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>+998959502203</t>
+          <t>+998997273529</t>
         </is>
       </c>
       <c r="K422" t="inlineStr">
@@ -24474,12 +24474,12 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Nazarov SHuhratbek Sherzod ogli</t>
+          <t>Razzoqberganov Asror Erkaboy o'g'li</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Inson resurslarini boshqarish</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -24494,44 +24494,44 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>AD9259094</t>
+          <t>AD2987496</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>51506085180054</t>
+          <t>52502077160012</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>Andijon viloyati</t>
+          <t>Toshkent shahri</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>Shahrixon tuman</t>
+          <t>Mirzo Ulugʻbek tumani</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>998951200052</t>
+          <t>998914322126</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>+998997273529</t>
+          <t>+998900003781</t>
         </is>
       </c>
       <c r="K423" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-23</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Razzoqberganov Asror Erkaboy o'g'li</t>
+          <t>Abdusattorov Bekzod</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -24541,7 +24541,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>O'zbek tili</t>
+          <t>Rus tili</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -24551,12 +24551,12 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>AD2987496</t>
+          <t>AD2560489</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>52502077160012</t>
+          <t>52509076180045</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
@@ -24566,17 +24566,17 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>Mirzo Ulugʻbek tumani</t>
+          <t>Sergeli tumani</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>998914322126</t>
+          <t>998933329491</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>+998900003781</t>
+          <t>+998933329491</t>
         </is>
       </c>
       <c r="K424" t="inlineStr">
@@ -24588,17 +24588,17 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Abdusattorov Bekzod</t>
+          <t>Musulmonova Madina Shavkat qizi</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Inson resurslarini boshqarish</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Rus tili</t>
+          <t>O'zbek tili</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -24608,32 +24608,32 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>AD2560489</t>
+          <t>AB7120141</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>52509076180045</t>
+          <t>62404005630051</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>Toshkent shahri</t>
+          <t>Qashqadaryo viloyati</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>Sergeli tumani</t>
+          <t>Qamashi tumani</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>998933329491</t>
+          <t>998886779877</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>+998933329491</t>
+          <t>+998886779877</t>
         </is>
       </c>
       <c r="K425" t="inlineStr">
@@ -24645,12 +24645,12 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Musulmonova Madina Shavkat qizi</t>
+          <t>Samiyeva Dildora Teshayevna</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Inson resurslarini boshqarish</t>
+          <t>Psixologiya</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -24665,32 +24665,32 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>AB7120141</t>
+          <t>AD2757324</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>62404005630051</t>
+          <t>43003881000104</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>Qashqadaryo viloyati</t>
+          <t>Toshkent shahri</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>Qamashi tumani</t>
+          <t>Chilonzor tumani</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>998886779877</t>
+          <t>998939677003</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>+998886779877</t>
+          <t>+998974043307</t>
         </is>
       </c>
       <c r="K426" t="inlineStr">
@@ -24702,12 +24702,12 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Samiyeva Dildora Teshayevna</t>
+          <t>Ruzmetova Gulasal</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Psixologiya</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -24722,49 +24722,49 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>AD2757324</t>
+          <t>AE1255796</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>43003881000104</t>
+          <t>41808987190027</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>Toshkent shahri</t>
+          <t>Xorazm viloyati</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>Chilonzor tumani</t>
+          <t>Urganch shahri</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>998939677003</t>
+          <t>998995550235</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>+998974043307</t>
+          <t>+998995550235</t>
         </is>
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-25</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Ruzmetova Gulasal</t>
+          <t>Lolashev Shahzod Ahmad O'g'li</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Inson resurslarini boshqarish</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -24779,32 +24779,32 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>AE1255796</t>
+          <t>AC1494049</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>41808987190027</t>
+          <t>52802025610014</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>Xorazm viloyati</t>
+          <t>Qashqadaryo viloyati</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>Urganch shahri</t>
+          <t>Dehqonobod tumani</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>998995550235</t>
+          <t>998770261713</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>+998995550235</t>
+          <t>+998770261713</t>
         </is>
       </c>
       <c r="K428" t="inlineStr">
@@ -24816,12 +24816,12 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Lolashev Shahzod Ahmad O'g'li</t>
+          <t>Ermatova Zaynab Rahmatillo qizi</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Inson resurslarini boshqarish</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -24836,32 +24836,32 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>AC1494049</t>
+          <t>AD6867685</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>52802025610014</t>
+          <t>62209076590026</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>Qashqadaryo viloyati</t>
+          <t>Toshkent shahri</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>Dehqonobod tumani</t>
+          <t>Chilonzor tumani</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>998770261713</t>
+          <t>998908071903</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>+998770261713</t>
+          <t>+998958917282</t>
         </is>
       </c>
       <c r="K429" t="inlineStr">
@@ -24873,12 +24873,12 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Ermatova Zaynab Rahmatillo qizi</t>
+          <t>Serkebaeva Feruza Sabit qizi</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Psixologiya</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -24893,32 +24893,32 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>AD6867685</t>
+          <t>AD3829042</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>62209076590026</t>
+          <t>62206076740048</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>Toshkent shahri</t>
+          <t>Toshkent viloyati</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>Chilonzor tumani</t>
+          <t>Yuqori Chirchiq tumani</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>998908071903</t>
+          <t>998930021618</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>+998958917282</t>
+          <t>+998995380175</t>
         </is>
       </c>
       <c r="K430" t="inlineStr">
@@ -24930,12 +24930,12 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Serkebaeva Feruza Sabit qizi</t>
+          <t>Boltayev Muhammad Shokir ogli</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Psixologiya</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -24950,32 +24950,32 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>AD3829042</t>
+          <t>AC1846105</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>62206076740048</t>
+          <t>52109015620025</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>Toshkent viloyati</t>
+          <t>Qashqadaryo viloyati</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>Yuqori Chirchiq tumani</t>
+          <t>Koʻkdala tumani</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>998930021618</t>
+          <t>79059076746</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>+998995380175</t>
+          <t>+998931780901</t>
         </is>
       </c>
       <c r="K431" t="inlineStr">
@@ -24987,12 +24987,12 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Boltayev Muhammad Shokir ogli</t>
+          <t>Xusanova Muxsina Xusan qizi</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Hayot faoliyati xavfsizligi</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -25007,32 +25007,32 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>AC1846105</t>
+          <t>AD5216772</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>52109015620025</t>
+          <t>61608066860012</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>Qashqadaryo viloyati</t>
+          <t>Toshkent viloyati</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>Koʻkdala tumani</t>
+          <t>Qibray tumani</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>79059076746</t>
+          <t>998993298483</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>+998931780901</t>
+          <t>+998993748483</t>
         </is>
       </c>
       <c r="K432" t="inlineStr">
@@ -25044,12 +25044,12 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Xusanova Muxsina Xusan qizi</t>
+          <t>Ismoilova Ziyoda Gulomjon qizi</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Hayot faoliyati xavfsizligi</t>
+          <t>Psixologiya</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -25064,12 +25064,12 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>AD5216772</t>
+          <t>AD1806101</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>61608066860012</t>
+          <t>62509066620024</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
@@ -25084,12 +25084,12 @@
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>998993298483</t>
+          <t>998938076529</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>+998993748483</t>
+          <t>+998998076529</t>
         </is>
       </c>
       <c r="K433" t="inlineStr">
@@ -25101,12 +25101,12 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Ismoilova Ziyoda Gulomjon qizi</t>
+          <t>Tulaganov Izattilla</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Psixologiya</t>
+          <t>Mehnat muhofazasi va texnika xavfsizligi</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -25121,32 +25121,32 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>AD1806101</t>
+          <t>AD1737814</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>62509066620024</t>
+          <t>31301876500017</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>Toshkent viloyati</t>
+          <t>Toshkent shahri</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>Qibray tumani</t>
+          <t>Yashnaobod tumani</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>998938076529</t>
+          <t>998930375050</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>+998998076529</t>
+          <t>+998930375050</t>
         </is>
       </c>
       <c r="K434" t="inlineStr">
@@ -25158,12 +25158,12 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Tulaganov Izattilla</t>
+          <t>Erkinov Jasur Erdonovich</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Mehnat muhofazasi va texnika xavfsizligi</t>
+          <t>Hayot faoliyati xavfsizligi</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -25178,32 +25178,32 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>AD1737814</t>
+          <t>AD6155474</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>31301876500017</t>
+          <t>51601085360000</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>Toshkent shahri</t>
+          <t>Buxoro viloyati</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>Yashnaobod tumani</t>
+          <t>Shofirkon tumani</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>998930375050</t>
+          <t>+998993508539</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>+998930375050</t>
+          <t>+998947609999</t>
         </is>
       </c>
       <c r="K435" t="inlineStr">
@@ -25215,12 +25215,12 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Erkinov Jasur Erdonovich</t>
+          <t>Davronov Doston Damirovich</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Hayot faoliyati xavfsizligi</t>
+          <t>Mehnat muhofazasi va texnika xavfsizligi</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -25235,12 +25235,12 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>AD6155474</t>
+          <t>AD7968118</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>51601085360000</t>
+          <t>51406075360023</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
@@ -25260,7 +25260,7 @@
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>+998947609999</t>
+          <t>+998973096969</t>
         </is>
       </c>
       <c r="K436" t="inlineStr">
@@ -25272,7 +25272,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Davronov Doston Damirovich</t>
+          <t>Abdusalomov Samandarbek Bobur ogli</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -25292,32 +25292,32 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>AD7968118</t>
+          <t>AD8969954</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>51406075360023</t>
+          <t>51402076380028</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>Buxoro viloyati</t>
+          <t>Sirdaryo viloyati</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>Shofirkon tumani</t>
+          <t>Oqoltin tumani</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>+998993508539</t>
+          <t>998888950207</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>+998973096969</t>
+          <t>+998940578004</t>
         </is>
       </c>
       <c r="K437" t="inlineStr">
@@ -25329,12 +25329,12 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Abdusalomov Samandarbek Bobur ogli</t>
+          <t>Qurbonov Dilshod</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Mehnat muhofazasi va texnika xavfsizligi</t>
+          <t>Ijtimoiy ish</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -25349,32 +25349,32 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>AD8969954</t>
+          <t>AC2293485</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>51402076380028</t>
+          <t>51308045360010</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>Sirdaryo viloyati</t>
+          <t>Buxoro viloyati</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>Oqoltin tumani</t>
+          <t>Shofirkon tumani</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>998888950207</t>
+          <t>998997051386</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>+998940578004</t>
+          <t>+998888670039</t>
         </is>
       </c>
       <c r="K438" t="inlineStr">
@@ -25386,12 +25386,12 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Qurbonov Dilshod</t>
+          <t>Sulaymonova Farida</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Ijtimoiy ish</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -25406,12 +25406,12 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>AC2293485</t>
+          <t>AC1797340</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>51308045360010</t>
+          <t>62302025360049</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
@@ -25431,7 +25431,7 @@
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>+998888670039</t>
+          <t>+998944550223</t>
         </is>
       </c>
       <c r="K439" t="inlineStr">
@@ -25443,7 +25443,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Sulaymonova Farida</t>
+          <t>Gulyamov Shavkat Sharafovich</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -25453,7 +25453,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>O'zbek tili</t>
+          <t>Rus tili</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -25463,32 +25463,32 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>AC1797340</t>
+          <t>AD3304690</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>62302025360049</t>
+          <t>51305076600023</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>Buxoro viloyati</t>
+          <t>Toshkent shahri</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>Shofirkon tumani</t>
+          <t>Mirzo Ulugʻbek tumani</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>998997051386</t>
+          <t>998998229911</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>+998944550223</t>
+          <t>+998998229911</t>
         </is>
       </c>
       <c r="K440" t="inlineStr">
@@ -25500,17 +25500,17 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Gulyamov Shavkat Sharafovich</t>
+          <t>Jurayev azamxon</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Bugalteriya hisobi</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Rus tili</t>
+          <t>O'zbek tili</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -25520,32 +25520,32 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>AD3304690</t>
+          <t>AD5272257</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>51305076600023</t>
+          <t>51006075670043</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>Toshkent shahri</t>
+          <t>Qashqadaryo viloyati</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>Mirzo Ulugʻbek tumani</t>
+          <t>Koson tumani</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>998998229911</t>
+          <t>998937101882</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>+998998229911</t>
+          <t>+998880120242</t>
         </is>
       </c>
       <c r="K441" t="inlineStr">
@@ -25557,17 +25557,17 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Jurayev azamxon</t>
+          <t>Nurmatova Latifa Yuldashevna</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Bugalteriya hisobi</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>O'zbek tili</t>
+          <t>Rus tili</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -25577,32 +25577,32 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>AD5272257</t>
+          <t>AD1415960</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>51006075670043</t>
+          <t>62904066180013</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>Qashqadaryo viloyati</t>
+          <t>Samarqand viloyati</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>Koson tumani</t>
+          <t>Samarqand shahri</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>998937101882</t>
+          <t>79951587430</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>+998880120242</t>
+          <t>+998910306141</t>
         </is>
       </c>
       <c r="K442" t="inlineStr">
@@ -25614,7 +25614,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Nurmatova Latifa Yuldashevna</t>
+          <t>Hazratov Mirazizjon Shahobiddin ogli</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -25624,7 +25624,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Rus tili</t>
+          <t>O'zbek tili</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -25634,44 +25634,44 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>AD1415960</t>
+          <t>AD8821344</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>62904066180013</t>
+          <t>51705076500033</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>Samarqand viloyati</t>
+          <t>Toshkent shahri</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>Samarqand shahri</t>
+          <t>Shayxontohur tumani</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>79951587430</t>
+          <t>998997858555</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>+998910306141</t>
+          <t>+998980010604</t>
         </is>
       </c>
       <c r="K443" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Hazratov Mirazizjon Shahobiddin ogli</t>
+          <t>Soatov Dilshodbek Otabek</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -25691,32 +25691,32 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>AD8821344</t>
+          <t>AD5803916</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>51705076500033</t>
+          <t>50209066220024</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>Toshkent shahri</t>
+          <t>Surxondaryo viloyati</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>Shayxontohur tumani</t>
+          <t>Muzrabot tumani</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t>998997858555</t>
+          <t>998932318131</t>
         </is>
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>+998980010604</t>
+          <t>+998932318131</t>
         </is>
       </c>
       <c r="K444" t="inlineStr">
@@ -25728,7 +25728,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Soatov Dilshodbek Otabek</t>
+          <t>Abdullayev Abdurahmon Xikmatillo Ugli</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -25748,32 +25748,32 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>AD5803916</t>
+          <t>AD9360444</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>50209066220024</t>
+          <t>51408076060012</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>Surxondaryo viloyati</t>
+          <t>Samarqand viloyati</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>Muzrabot tumani</t>
+          <t>Kattaqoʻrgʻon tumani</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>998932318131</t>
+          <t>998905058986</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>+998932318131</t>
+          <t>+998901969434</t>
         </is>
       </c>
       <c r="K445" t="inlineStr">
@@ -25785,7 +25785,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Abdullayev Abdurahmon Xikmatillo Ugli</t>
+          <t>Zaynidinov Ziyoviddin</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -25805,32 +25805,32 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>AD9360444</t>
+          <t>AD6282282</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>51408076060012</t>
+          <t>52910076820044</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>Samarqand viloyati</t>
+          <t>Toshkent viloyati</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>Kattaqoʻrgʻon tumani</t>
+          <t>Yangiyoʻl tumani</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>998905058986</t>
+          <t>998881502218</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>+998901969434</t>
+          <t>+998975388821</t>
         </is>
       </c>
       <c r="K446" t="inlineStr">
@@ -25842,7 +25842,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Zaynidinov Ziyoviddin</t>
+          <t>Davronov Orifjon Zarifjonivich</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -25862,32 +25862,32 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>AD6282282</t>
+          <t>AD9113330</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>52910076820044</t>
+          <t>50110076240048</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>Toshkent viloyati</t>
+          <t>Surxondaryo viloyati</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>Yangiyoʻl tumani</t>
+          <t>Jarqoʻrgʻon tumani</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>998881502218</t>
+          <t>998919092333</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>+998975388821</t>
+          <t>+998978500011</t>
         </is>
       </c>
       <c r="K447" t="inlineStr">
@@ -25899,7 +25899,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Davronov Orifjon Zarifjonivich</t>
+          <t>Xushnudov Xushnudbek Jasurbek ogli</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -25919,32 +25919,32 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>AD9113330</t>
+          <t>AD5122884</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>50110076240048</t>
+          <t>32107967180022</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>Surxondaryo viloyati</t>
+          <t>Xorazm viloyati</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>Jarqoʻrgʻon tumani</t>
+          <t>Yangiariq tumani</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>998919092333</t>
+          <t>998995001772</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>+998978500011</t>
+          <t>+998937707908</t>
         </is>
       </c>
       <c r="K448" t="inlineStr">
@@ -25956,7 +25956,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Xushnudov Xushnudbek Jasurbek ogli</t>
+          <t>Olimov Mironshoh Ikromjon ogli</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -25976,44 +25976,44 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>AD5122884</t>
+          <t>AD8591688</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>32107967180022</t>
+          <t>50904085310021</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>Xorazm viloyati</t>
+          <t>Buxoro viloyati</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>Yangiariq tumani</t>
+          <t>Gʻijduvon tumani</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>998995001772</t>
+          <t>998996878247</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>+998937707908</t>
+          <t>+998914140046</t>
         </is>
       </c>
       <c r="K449" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Olimov Mironshoh Ikromjon ogli</t>
+          <t>Boltayev Afrozbek Shamsiddin ogli</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -26033,32 +26033,32 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>AD8591688</t>
+          <t>AD7494169</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>50904085310021</t>
+          <t>52908075740104</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>Buxoro viloyati</t>
+          <t>Qashqadaryo viloyati</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>Gʻijduvon tumani</t>
+          <t>Qarshi tumani</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>998996878247</t>
+          <t>998939087077</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>+998914140046</t>
+          <t>+998939011117</t>
         </is>
       </c>
       <c r="K450" t="inlineStr">
@@ -26070,7 +26070,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Boltayev Afrozbek Shamsiddin ogli</t>
+          <t>Bahodir Buxorov Xayrullo o'g'li</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -26090,32 +26090,32 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>AD7494169</t>
+          <t>AD5490107</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>52908075740104</t>
+          <t>51611076590092</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>Qashqadaryo viloyati</t>
+          <t>Toshkent shahri</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>Qarshi tumani</t>
+          <t>Mirobod tumani</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>998939087077</t>
+          <t>998884921611</t>
         </is>
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>+998939011117</t>
+          <t>+998974455663</t>
         </is>
       </c>
       <c r="K451" t="inlineStr">
@@ -26127,7 +26127,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Bahodir Buxorov Xayrullo o'g'li</t>
+          <t>Akatova Yaxshigul Usmon qizi</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -26137,7 +26137,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>O'zbek tili</t>
+          <t>Rus tili</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -26147,12 +26147,12 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>AD5490107</t>
+          <t>AD9706671</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>51611076590092</t>
+          <t>60305086600062</t>
         </is>
       </c>
       <c r="G452" t="inlineStr">
@@ -26162,17 +26162,17 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>Mirobod tumani</t>
+          <t>Mirzo Ulugʻbek tumani</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t>998884921611</t>
+          <t>998977353305</t>
         </is>
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>+998974455663</t>
+          <t>+998977353305</t>
         </is>
       </c>
       <c r="K452" t="inlineStr">
@@ -26184,7 +26184,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Akatova Yaxshigul Usmon qizi</t>
+          <t>Isloomquolv Iqrorbek ibrohimjon o'g'il</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Rus tili</t>
+          <t>O'zbek tili</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -26204,12 +26204,12 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>AD9706671</t>
+          <t>AD3123634</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>60305086600062</t>
+          <t>50309067020064</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
@@ -26219,17 +26219,17 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>Mirzo Ulugʻbek tumani</t>
+          <t>Yunusobod tumani</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>998977353305</t>
+          <t>998932590309</t>
         </is>
       </c>
       <c r="J453" t="inlineStr">
         <is>
-          <t>+998977353305</t>
+          <t>+998932590309</t>
         </is>
       </c>
       <c r="K453" t="inlineStr">
@@ -26241,7 +26241,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Isloomquolv Iqrorbek ibrohimjon o'g'il</t>
+          <t>Narzullayeva Shaxrizoda Jamshidovna</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -26261,32 +26261,32 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>AD3123634</t>
+          <t>AD7580233</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>50309067020064</t>
+          <t>60903086180025</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>Toshkent shahri</t>
+          <t>Samarqand viloyati</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>Yunusobod tumani</t>
+          <t>Samarqand shahri</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t>998932590309</t>
+          <t>998906561315</t>
         </is>
       </c>
       <c r="J454" t="inlineStr">
         <is>
-          <t>+998932590309</t>
+          <t>+998906561315</t>
         </is>
       </c>
       <c r="K454" t="inlineStr">
@@ -26298,7 +26298,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Narzullayeva Shaxrizoda Jamshidovna</t>
+          <t>Turganova Zuhra Karimboy qizi</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -26318,32 +26318,32 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>AD7580233</t>
+          <t>AD2343678</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>60903086180025</t>
+          <t>61101077350069</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>Samarqand viloyati</t>
+          <t>Toshkent shahri</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>Samarqand shahri</t>
+          <t>Chilonzor tumani</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>998906561315</t>
+          <t>998993561772</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>+998906561315</t>
+          <t>+998884321707</t>
         </is>
       </c>
       <c r="K455" t="inlineStr">
@@ -26355,7 +26355,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Turganova Zuhra Karimboy qizi</t>
+          <t>Toshboyev Bekzod Ilyos ogli</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -26375,44 +26375,44 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>AD2343678</t>
+          <t>AD5293603</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>61101077350069</t>
+          <t>52909075650033</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>Toshkent shahri</t>
+          <t>Qashqadaryo viloyati</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>Chilonzor tumani</t>
+          <t>Qarshi tumani</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>998993561772</t>
+          <t>998883120506</t>
         </is>
       </c>
       <c r="J456" t="inlineStr">
         <is>
-          <t>+998884321707</t>
+          <t>+998972915018</t>
         </is>
       </c>
       <c r="K456" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Toshboyev Bekzod Ilyos ogli</t>
+          <t>Yaxshiboyeva Aziza Sayfullo qizi</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -26432,32 +26432,32 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>AD5293603</t>
+          <t>AB7577027</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>52909075650033</t>
+          <t>61804016390013</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>Qashqadaryo viloyati</t>
+          <t>Sirdaryo viloyati</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>Qarshi tumani</t>
+          <t>Boyovut tumani</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t>998883120506</t>
+          <t>998938110104</t>
         </is>
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>+998972915018</t>
+          <t>+998938110104</t>
         </is>
       </c>
       <c r="K457" t="inlineStr">
@@ -26469,7 +26469,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Yaxshiboyeva Aziza Sayfullo qizi</t>
+          <t>Azmedjonov Shamshod Ulugbek ugli</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -26479,7 +26479,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>O'zbek tili</t>
+          <t>Rus tili</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -26489,54 +26489,54 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>AB7577027</t>
+          <t>AD5729860</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>61804016390013</t>
+          <t>52604075540044</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>Sirdaryo viloyati</t>
+          <t>Jizzax viloyati</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>Boyovut tumani</t>
+          <t>Jizzax shahri</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>998938110104</t>
+          <t>998918880049</t>
         </is>
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t>+998938110104</t>
+          <t>+998900254900</t>
         </is>
       </c>
       <c r="K458" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Azmedjonov Shamshod Ulugbek ugli</t>
+          <t>Shonazarova Surayyo Shamsiddinovna</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Psixologiya</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Rus tili</t>
+          <t>O'zbek tili</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -26546,32 +26546,32 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>AD5729860</t>
+          <t>AE2575292</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>52604075540044</t>
+          <t>40207902640101</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>Jizzax viloyati</t>
+          <t>Toshkent viloyati</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>Jizzax shahri</t>
+          <t>Chirchiq shahri</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>998918880049</t>
+          <t>998334065663</t>
         </is>
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>+998900254900</t>
+          <t>+998931342107</t>
         </is>
       </c>
       <c r="K459" t="inlineStr">
@@ -26583,17 +26583,17 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Shonazarova Surayyo Shamsiddinovna</t>
+          <t>Abdullayev Abdullo Anvarjonovich</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Psixologiya</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>O'zbek tili</t>
+          <t>Rus tili</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -26603,32 +26603,32 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>AE2575292</t>
+          <t>AB3832239</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>40207902640101</t>
+          <t>51404006610012</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>Toshkent viloyati</t>
+          <t>Toshkent shahri</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>Chirchiq shahri</t>
+          <t>Olmazor tumani</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>998334065663</t>
+          <t>998991777766</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
         <is>
-          <t>+998931342107</t>
+          <t>+998909407476</t>
         </is>
       </c>
       <c r="K460" t="inlineStr">
@@ -26640,7 +26640,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Abdullayev Abdullo Anvarjonovich</t>
+          <t>Erkinova Zarinabonu Anvarjonovna</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -26660,12 +26660,12 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>AB3832239</t>
+          <t>AD9740368</t>
         </is>
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>51404006610012</t>
+          <t>62906026610079</t>
         </is>
       </c>
       <c r="G461" t="inlineStr">
@@ -26675,17 +26675,17 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>Olmazor tumani</t>
+          <t>Mirzo Ulugʻbek tumani</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
         <is>
-          <t>998991777766</t>
+          <t>998974882906</t>
         </is>
       </c>
       <c r="J461" t="inlineStr">
         <is>
-          <t>+998909407476</t>
+          <t>+998903713166</t>
         </is>
       </c>
       <c r="K461" t="inlineStr">
@@ -26697,17 +26697,17 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Erkinova Zarinabonu Anvarjonovna</t>
+          <t>Rahmonov Shoxjahon Sharof ogli</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Inson resurslarini boshqarish</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Rus tili</t>
+          <t>O'zbek tili</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -26717,32 +26717,32 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>AD9740368</t>
+          <t>AC0088106</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>62906026610079</t>
+          <t>50102026060068</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>Toshkent shahri</t>
+          <t>Samarqand viloyati</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>Mirzo Ulugʻbek tumani</t>
+          <t>Kattaqoʻrgʻon tumani</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>998974882906</t>
+          <t>998953273322</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>+998903713166</t>
+          <t>+998990922361</t>
         </is>
       </c>
       <c r="K462" t="inlineStr">
@@ -26754,12 +26754,12 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Rahmonov Shoxjahon Sharof ogli</t>
+          <t>Ismailov Avzal Hakim ugli</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Inson resurslarini boshqarish</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -26774,32 +26774,32 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>AC0088106</t>
+          <t>AD7435091</t>
         </is>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>50102026060068</t>
+          <t>51302085540018</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>Samarqand viloyati</t>
+          <t>Jizzax viloyati</t>
         </is>
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>Kattaqoʻrgʻon tumani</t>
+          <t>Jizzax shahri</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
         <is>
-          <t>998953273322</t>
+          <t>998912272278</t>
         </is>
       </c>
       <c r="J463" t="inlineStr">
         <is>
-          <t>+998990922361</t>
+          <t>+998912272278</t>
         </is>
       </c>
       <c r="K463" t="inlineStr">
@@ -26811,7 +26811,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Ismailov Avzal Hakim ugli</t>
+          <t>Abdullaev Azizbek Akobirovich</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -26831,32 +26831,32 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>AD7435091</t>
+          <t>AB9284235</t>
         </is>
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>51302085540018</t>
+          <t>50804025260039</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>Jizzax viloyati</t>
+          <t>Buxoro viloyati</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>Jizzax shahri</t>
+          <t>Buxoro tumani</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t>998912272278</t>
+          <t>998997011210</t>
         </is>
       </c>
       <c r="J464" t="inlineStr">
         <is>
-          <t>+998912272278</t>
+          <t>+998900807557</t>
         </is>
       </c>
       <c r="K464" t="inlineStr">
@@ -26868,12 +26868,12 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Abdullaev Azizbek Akobirovich</t>
+          <t>Atabayev Umarbek Umirbekovich</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Hayot faoliyati xavfsizligi</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -26888,32 +26888,32 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>AB9284235</t>
+          <t>AD5294160</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>50804025260039</t>
+          <t>52109077190034</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>Buxoro viloyati</t>
+          <t>Xorazm viloyati</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>Buxoro tumani</t>
+          <t>Urganch shahri</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
         <is>
-          <t>998997011210</t>
+          <t>998998657077</t>
         </is>
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>+998900807557</t>
+          <t>+998974515101</t>
         </is>
       </c>
       <c r="K465" t="inlineStr">
@@ -26925,12 +26925,12 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Atabayev Umarbek Umirbekovich</t>
+          <t>Mamasodiqov Dilyor Dilmurodovich</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Hayot faoliyati xavfsizligi</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -26945,32 +26945,32 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>AD5294160</t>
+          <t>AD3265008</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>52109077190034</t>
+          <t>52203076840067</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>Xorazm viloyati</t>
+          <t>Toshkent viloyati</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>Urganch shahri</t>
+          <t>Angren shahri</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>998998657077</t>
+          <t>998936284656</t>
         </is>
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>+998974515101</t>
+          <t>+998936284656</t>
         </is>
       </c>
       <c r="K466" t="inlineStr">
@@ -26982,7 +26982,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Mamasodiqov Dilyor Dilmurodovich</t>
+          <t>rajabov bekzodbek sharofaddinovich</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -26992,7 +26992,7 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>O'zbek tili</t>
+          <t>Rus tili</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -27002,32 +27002,32 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>AD3265008</t>
+          <t>AD6646179</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>52203076840067</t>
+          <t>50607077120045</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>Toshkent viloyati</t>
+          <t>Xorazm viloyati</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>Angren shahri</t>
+          <t>Qoʻshkoʻpir tumani</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>998936284656</t>
+          <t>998910050915</t>
         </is>
       </c>
       <c r="J467" t="inlineStr">
         <is>
-          <t>+998936284656</t>
+          <t>+998951730180</t>
         </is>
       </c>
       <c r="K467" t="inlineStr">
@@ -27039,17 +27039,17 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>rajabov bekzodbek sharofaddinovich</t>
+          <t>Esonov Suhrobjon</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Psixologiya</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Rus tili</t>
+          <t>O'zbek tili</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -27059,32 +27059,32 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>AD6646179</t>
+          <t>AD5719970</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>50607077120045</t>
+          <t>51511076580032</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>Xorazm viloyati</t>
+          <t>Toshkent shahri</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>Qoʻshkoʻpir tumani</t>
+          <t>Yashnaobod tumani</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>998910050915</t>
+          <t>998901162980</t>
         </is>
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>+998951730180</t>
+          <t>+998901162980</t>
         </is>
       </c>
       <c r="K468" t="inlineStr">
@@ -27096,12 +27096,12 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Esonov Suhrobjon</t>
+          <t>Komilov Xasan</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Psixologiya</t>
+          <t>Inson resurslarini boshqarish</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -27116,32 +27116,32 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>AD5719970</t>
+          <t>AD5600712</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>51511076580032</t>
+          <t>31501965680055</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>Toshkent shahri</t>
+          <t>Qashqadaryo viloyati</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>Yashnaobod tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>998901162980</t>
+          <t>998990263130</t>
         </is>
       </c>
       <c r="J469" t="inlineStr">
         <is>
-          <t>+998901162980</t>
+          <t>+998990263130</t>
         </is>
       </c>
       <c r="K469" t="inlineStr">
@@ -27153,17 +27153,17 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Komilov Xasan</t>
+          <t>Maksudov Dilshod</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Inson resurslarini boshqarish</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>O'zbek tili</t>
+          <t>Rus tili</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -27173,32 +27173,32 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>AD5600712</t>
+          <t>AD6029202</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>31501965680055</t>
+          <t>52901086520121</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>Qashqadaryo viloyati</t>
+          <t>Toshkent shahri</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Yunusobod tumani</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>998990263130</t>
+          <t>998946530129</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>+998990263130</t>
+          <t>+998977100129</t>
         </is>
       </c>
       <c r="K470" t="inlineStr">
@@ -27210,7 +27210,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Maksudov Dilshod</t>
+          <t>Erkinova Gulsevar Behzod qizi</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -27220,7 +27220,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Rus tili</t>
+          <t>O'zbek tili</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -27230,32 +27230,32 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>AD6029202</t>
+          <t>AD4131232</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>52901086520121</t>
+          <t>60801075590029</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>Toshkent shahri</t>
+          <t>Qashqadaryo viloyati</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>Yunusobod tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>998946530129</t>
+          <t>998942692523</t>
         </is>
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>+998977100129</t>
+          <t>+998930498485</t>
         </is>
       </c>
       <c r="K471" t="inlineStr">
@@ -27267,7 +27267,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Erkinova Gulsevar Behzod qizi</t>
+          <t>Nurmuxammedova Nigina Toxirovna</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -27287,32 +27287,32 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>AD4131232</t>
+          <t>AC0576281</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>60801075590029</t>
+          <t>40405816480017</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>Qashqadaryo viloyati</t>
+          <t>Sirdaryo viloyati</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Yangiyer shahri</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>998942692523</t>
+          <t>998974446604</t>
         </is>
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>+998930498485</t>
+          <t>+998949578878</t>
         </is>
       </c>
       <c r="K472" t="inlineStr">
@@ -27324,7 +27324,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Nurmuxammedova Nigina Toxirovna</t>
+          <t>Teshaboyev Tamerlan Zafar o'g'li</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -27334,7 +27334,7 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>O'zbek tili</t>
+          <t>Rus tili</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -27344,44 +27344,44 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>AC0576281</t>
+          <t>AD5550317</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>40405816480017</t>
+          <t>51804077040075</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>Sirdaryo viloyati</t>
+          <t>Fargona viloyati</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>Yangiyer shahri</t>
+          <t>Qoʻshtepa tumani</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>998974446604</t>
+          <t>+998902318401</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>+998949578878</t>
+          <t>+998888688999</t>
         </is>
       </c>
       <c r="K473" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-30</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Teshaboyev Tamerlan Zafar o'g'li</t>
+          <t>Umarqulov Jasurbek Jumaboy o'g'li</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -27391,7 +27391,7 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Rus tili</t>
+          <t>O'zbek tili</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
@@ -27401,44 +27401,44 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>AD5550317</t>
+          <t>AB9822494</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>51804077040075</t>
+          <t>50804016420022</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>Fargona viloyati</t>
+          <t>Toshkent shahri</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>Qoʻshtepa tumani</t>
+          <t>Sergeli tumani</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>+998902318401</t>
+          <t>998941200071</t>
         </is>
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>+998888688999</t>
+          <t>+998949112120</t>
         </is>
       </c>
       <c r="K474" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-31</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Umarqulov Jasurbek Jumaboy o'g'li</t>
+          <t>Usmonqulova Malika Baxtiyor qizi</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -27448,7 +27448,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>O'zbek tili</t>
+          <t>Rus tili</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -27458,54 +27458,54 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>AB9822494</t>
+          <t>AD7340826</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>50804016420022</t>
+          <t>62401075650017</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>Toshkent shahri</t>
+          <t>Qashqadaryo viloyati</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>Sergeli tumani</t>
+          <t>Qarshi tumani</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t>998941200071</t>
+          <t>998905183285</t>
         </is>
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>+998949112120</t>
+          <t>+998773290124</t>
         </is>
       </c>
       <c r="K475" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-02</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Usmonqulova Malika Baxtiyor qizi</t>
+          <t>To'rayev Olmosbek Sanjar o'g'li</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Yurisprudensiya</t>
+          <t>Bugalteriya hisobi</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Rus tili</t>
+          <t>O'zbek tili</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -27515,49 +27515,49 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>AD7340826</t>
+          <t>AD6260739</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>62401075650017</t>
+          <t>52010075590125</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>Qashqadaryo viloyati</t>
+          <t>Toshkent shahri</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>Qarshi tumani</t>
+          <t>Yangihayot tumani</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>998905183285</t>
+          <t>+998909771840</t>
         </is>
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>+998773290124</t>
+          <t>+998947526061</t>
         </is>
       </c>
       <c r="K476" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>To'rayev Olmosbek Sanjar o'g'li</t>
+          <t>Mahkamov Doniyor Baxtiyer o'g'li</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Bugalteriya hisobi</t>
+          <t>Menejment</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -27572,12 +27572,12 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>AD6260739</t>
+          <t>AD2721331</t>
         </is>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>52010075590125</t>
+          <t>30601966600067</t>
         </is>
       </c>
       <c r="G477" t="inlineStr">
@@ -27587,17 +27587,17 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>Yangihayot tumani</t>
+          <t>Mirzo Ulugʻbek tumani</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
         <is>
-          <t>+998909771840</t>
+          <t>998933231850</t>
         </is>
       </c>
       <c r="J477" t="inlineStr">
         <is>
-          <t>+998947526061</t>
+          <t>+998933231850</t>
         </is>
       </c>
       <c r="K477" t="inlineStr">
@@ -27609,12 +27609,12 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Mahkamov Doniyor Baxtiyer o'g'li</t>
+          <t>Abdullayev Ogabek Abdujalil  ogli</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Menejment</t>
+          <t>Yurisprudensiya</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -27629,37 +27629,550 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>AD2721331</t>
+          <t>AE3450877</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>30601966600067</t>
+          <t>53101075440112</t>
         </is>
       </c>
       <c r="G478" t="inlineStr">
         <is>
+          <t>Jizzax viloyati</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>Gʻallaorol tumani</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>998942377804</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>+998941960005</t>
+        </is>
+      </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Karimjonov Oybek Alisherovich</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Ijtimoiy ish</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>AD9609610</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>51303080005032</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
           <t>Toshkent shahri</t>
         </is>
       </c>
-      <c r="H478" t="inlineStr">
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>Yashnaobod tumani</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>998949990199</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>+998949990199</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Akmaljonov Odiljon Ahmadovich</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Ijtimoiy ish</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>AD7428515</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>52405086580029</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>Yashnaobod tumani</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>998930678551</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>+998930678551</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Ochilboyev Nuriddin Sirojiddin o'g'li</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>AE2057790</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>50201075440068</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>Jizzax viloyati</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>Gʻallaorol tumani</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>998947908277</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>+998872200219</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Qorsboyev Bekzod Qarshiboyevich</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>AD5895003</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>32002876390011</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
         <is>
           <t>Mirzo Ulugʻbek tumani</t>
         </is>
       </c>
-      <c r="I478" t="inlineStr">
-        <is>
-          <t>998933231850</t>
-        </is>
-      </c>
-      <c r="J478" t="inlineStr">
-        <is>
-          <t>+998933231850</t>
-        </is>
-      </c>
-      <c r="K478" t="inlineStr">
-        <is>
-          <t>2025-09-03</t>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>998979050070</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>+998979050070</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Husanova Ruxshona</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Ijtimoiy ish</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>AD0689711</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>61608056060024</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>Mirzo Ulugʻbek tumani</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>998508841601</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>+998949576414</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Yoldoshev Sunnatillo</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>AD2149470</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>50603060005153</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>Fargona viloyati</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>Qo‘qon shahri</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>998916885571</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>+998916885571</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Qodirov shohxusrav</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>AD4483287</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>50907077050017</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>Fargona viloyati</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>Qo‘qon shahri</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>998944447531</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>+998940073032</t>
+        </is>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Xudoynazarov Sherdor</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Ijtimoiy ish</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>AB9808208</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>52904026560063</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>Chilonzor tumani</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>998991009955</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>+998887554343</t>
+        </is>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>davronov abdulaziz asqarali ogli</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>AD9036702</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>52808075610017</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>Qashqadaryo viloyati</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>Dehqonobod tumani</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>998942377545</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>+998942377545</t>
+        </is>
+      </c>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
         </is>
       </c>
     </row>

--- a/file_service/qabul.xlsx
+++ b/file_service/qabul.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M487"/>
+  <dimension ref="A1:M490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.42578125" customWidth="1" min="1" max="1"/>
@@ -28176,6 +28176,177 @@
         </is>
       </c>
     </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Boboxonov Sultonmurod Elbursovich</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Rus tili</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>AD1630655</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>52811046350010</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>Surxondaryo viloyati</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>Termiz tumani</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>998900115997</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>+998909177807</t>
+        </is>
+      </c>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Abdujalalova Bahor Abduhamid qizi</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Yurisprudensiya</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Rus tili</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>AD7514213</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>61505086840074</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>Toshkent viloyati</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>Angren shahri</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>998941681114</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>+998941681114</t>
+        </is>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Ablatova Maftuna Alisher qizi</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Bugalteriya hisobi</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>O'zbek tili</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Kunduzgi</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>AD7780519</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>60710076540037</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>Toshkent shahri</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>Mirzo Ulugʻbek tumani</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>998901376236</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>+998958494858</t>
+        </is>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="D1:D66"/>
   <mergeCells count="1">
